--- a/party-comparison-updated-v83.xlsx
+++ b/party-comparison-updated-v83.xlsx
@@ -311,8 +311,178 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מדגם מעודכן</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. Maariv 28/10/2026 02:19 (maariv.co.il/news/elections-2026/article-1382036); </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">המשותפת </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">12 לפי סך הגוש הערבי (19) בכתבה</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מדגם מעודכן</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. Maariv 28/10/2026 02:19 (maariv.co.il/news/elections-2026/article-1382036); </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">המשותפת </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">11 לפי סך הגוש הערבי (18) בכתבה</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מדגם מעודכן </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">01:43. maariv.co.il/breaking-news/article-1382115 + </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מדגם ראשון ב</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">-ynet</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מדגם מעודכן (גוש נתניהו </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">62). Maariv 28/10/2026 02:19 (maariv.co.il/news/elections-2026/article-1382036); ynet.co.il/news/article/h1nq00srhme</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Maariv 28/10/2026 02:19 (maariv.co.il/news/elections-2026/article-1382036)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">מדגם ראשון (אין עדכון)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. ynet.co.il/news/elections2026/article/rks5sp03zx</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7380" uniqueCount="1834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="1852">
   <si>
     <t xml:space="preserve">מפלגה</t>
   </si>
@@ -7072,6 +7242,117 @@
     <t xml:space="preserve">מספר משיבים</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">חדשות </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מנו גבע</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">חדשות </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">המדד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כאן חדשות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דודי חסיד</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ערוץ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">שלמה פילבר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i24 news</t>
+  </si>
+  <si>
+    <t xml:space="preserve">צוריאל שרון</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ערוץ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">יצחק כ״ץ</t>
+  </si>
+  <si>
     <t xml:space="preserve">מנדטים</t>
   </si>
   <si>
@@ -7135,6 +7416,176 @@
   </si>
   <si>
     <t xml:space="preserve">הערה</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ש</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ס</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">רע</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">מ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ביחד </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">בנט</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">לפיד</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ישר</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">המילואימניקים</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">הכלכלית</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -47126,12 +47577,324 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -47140,6 +47903,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -47148,7 +47912,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47162,7 +47926,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1831</v>
+        <v>1844</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>1472</v>
@@ -47174,10 +47938,2818 @@
         <v>1807</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1832</v>
+        <v>1845</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1833</v>
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B2" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>27</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
+        <v>4</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
+        <v>23</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <f aca="false">IF($D2=0,0,$E2/$D2)</f>
+        <v>0.148148148148148</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2)</f>
+        <v>36</v>
+      </c>
+      <c r="I2" s="0" t="str">
+        <f aca="false">IF(AND($D2&gt;0,$H2=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
+        <v>6</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <f aca="false">IF($D3=0,0,$E3/$D3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3)</f>
+        <v>9</v>
+      </c>
+      <c r="I3" s="0" t="str">
+        <f aca="false">IF(AND($D3&gt;0,$H3=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B4" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
+        <v>7</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <f aca="false">IF($D4=0,0,$E4/$D4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4)</f>
+        <v>11</v>
+      </c>
+      <c r="I4" s="0" t="str">
+        <f aca="false">IF(AND($D4&gt;0,$H4=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B5" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>12</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
+        <v>8</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <f aca="false">IF($D5=0,0,$E5/$D5)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5)</f>
+        <v>10</v>
+      </c>
+      <c r="I5" s="0" t="str">
+        <f aca="false">IF(AND($D5&gt;0,$H5=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B6" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
+        <v>5</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <f aca="false">IF($D6=0,0,$E6/$D6)</f>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6)</f>
+        <v>20</v>
+      </c>
+      <c r="I6" s="0" t="str">
+        <f aca="false">IF(AND($D6&gt;0,$H6=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B7" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
+        <v>4</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
+        <v>5</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <f aca="false">IF($D7=0,0,$E7/$D7)</f>
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7)</f>
+        <v>20</v>
+      </c>
+      <c r="I7" s="0" t="str">
+        <f aca="false">IF(AND($D7&gt;0,$H7=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B8" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
+        <v>1</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
+        <v>5</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <f aca="false">IF($D8=0,0,$E8/$D8)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8)</f>
+        <v>18</v>
+      </c>
+      <c r="I8" s="0" t="str">
+        <f aca="false">IF(AND($D8&gt;0,$H8=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B9" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
+        <v>5</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <f aca="false">IF($D9=0,0,$E9/$D9)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9)</f>
+        <v>6</v>
+      </c>
+      <c r="I9" s="0" t="str">
+        <f aca="false">IF(AND($D9&gt;0,$H9=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B10" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
+        <v>4</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <f aca="false">IF($D10=0,0,$E10/$D10)</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10)</f>
+        <v>17</v>
+      </c>
+      <c r="I10" s="0" t="str">
+        <f aca="false">IF(AND($D10&gt;0,$H10=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B11" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>12</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
+        <v>6</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
+        <v>6</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <f aca="false">IF($D11=0,0,$E11/$D11)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11)</f>
+        <v>26</v>
+      </c>
+      <c r="I11" s="0" t="str">
+        <f aca="false">IF(AND($D11&gt;0,$H11=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B12" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>21</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
+        <v>11</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
+        <v>10</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <f aca="false">IF($D12=0,0,$E12/$D12)</f>
+        <v>0.523809523809524</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12)</f>
+        <v>40</v>
+      </c>
+      <c r="I12" s="0" t="str">
+        <f aca="false">IF(AND($D12&gt;0,$H12=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B13" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <f aca="false">IF($D13=0,0,$E13/$D13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13)</f>
+        <v>11</v>
+      </c>
+      <c r="I13" s="0" t="str">
+        <f aca="false">IF(AND($D13&gt;0,$H13=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B14" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <f aca="false">IF($D14=0,0,$E14/$D14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14)</f>
+        <v>20</v>
+      </c>
+      <c r="I14" s="0" t="str">
+        <f aca="false">IF(AND($D14&gt;0,$H14=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B15" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>27</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
+        <v>4</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
+        <v>23</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <f aca="false">IF($D15=0,0,$E15/$D15)</f>
+        <v>0.148148148148148</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15)</f>
+        <v>36</v>
+      </c>
+      <c r="I15" s="0" t="str">
+        <f aca="false">IF(AND($D15&gt;0,$H15=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B16" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
+        <v>6</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <f aca="false">IF($D16=0,0,$E16/$D16)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16)</f>
+        <v>9</v>
+      </c>
+      <c r="I16" s="0" t="str">
+        <f aca="false">IF(AND($D16&gt;0,$H16=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B17" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
+        <v>6</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <f aca="false">IF($D17=0,0,$E17/$D17)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17)</f>
+        <v>11</v>
+      </c>
+      <c r="I17" s="0" t="str">
+        <f aca="false">IF(AND($D17&gt;0,$H17=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B18" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>11</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
+        <v>2</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
+        <v>8</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <f aca="false">IF($D18=0,0,$E18/$D18)</f>
+        <v>0.181818181818182</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18)</f>
+        <v>10</v>
+      </c>
+      <c r="I18" s="0" t="str">
+        <f aca="false">IF(AND($D18&gt;0,$H18=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B19" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
+        <v>2</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
+        <v>5</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <f aca="false">IF($D19=0,0,$E19/$D19)</f>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19)</f>
+        <v>20</v>
+      </c>
+      <c r="I19" s="0" t="str">
+        <f aca="false">IF(AND($D19&gt;0,$H19=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B20" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
+        <v>4</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
+        <v>5</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <f aca="false">IF($D20=0,0,$E20/$D20)</f>
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20)</f>
+        <v>20</v>
+      </c>
+      <c r="I20" s="0" t="str">
+        <f aca="false">IF(AND($D20&gt;0,$H20=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B21" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
+        <v>1</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
+        <v>5</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <f aca="false">IF($D21=0,0,$E21/$D21)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21)</f>
+        <v>18</v>
+      </c>
+      <c r="I21" s="0" t="str">
+        <f aca="false">IF(AND($D21&gt;0,$H21=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B22" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
+        <v>5</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <f aca="false">IF($D22=0,0,$E22/$D22)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22)</f>
+        <v>6</v>
+      </c>
+      <c r="I22" s="0" t="str">
+        <f aca="false">IF(AND($D22&gt;0,$H22=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B23" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
+        <v>2</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
+        <v>4</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <f aca="false">IF($D23=0,0,$E23/$D23)</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23)</f>
+        <v>17</v>
+      </c>
+      <c r="I23" s="0" t="str">
+        <f aca="false">IF(AND($D23&gt;0,$H23=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B24" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>13</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
+        <v>6</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
+        <v>7</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <f aca="false">IF($D24=0,0,$E24/$D24)</f>
+        <v>0.461538461538462</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24)</f>
+        <v>26</v>
+      </c>
+      <c r="I24" s="0" t="str">
+        <f aca="false">IF(AND($D24&gt;0,$H24=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B25" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>22</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
+        <v>11</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
+        <v>11</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <f aca="false">IF($D25=0,0,$E25/$D25)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25)</f>
+        <v>40</v>
+      </c>
+      <c r="I25" s="0" t="str">
+        <f aca="false">IF(AND($D25&gt;0,$H25=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B26" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <f aca="false">IF($D26=0,0,$E26/$D26)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26)</f>
+        <v>11</v>
+      </c>
+      <c r="I26" s="0" t="str">
+        <f aca="false">IF(AND($D26&gt;0,$H26=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B27" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <f aca="false">IF($D27=0,0,$E27/$D27)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27)</f>
+        <v>20</v>
+      </c>
+      <c r="I27" s="0" t="str">
+        <f aca="false">IF(AND($D27&gt;0,$H27=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B28" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>27</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
+        <v>4</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
+        <v>23</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <f aca="false">IF($D28=0,0,$E28/$D28)</f>
+        <v>0.148148148148148</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28)</f>
+        <v>36</v>
+      </c>
+      <c r="I28" s="0" t="str">
+        <f aca="false">IF(AND($D28&gt;0,$H28=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B29" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
+        <v>6</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <f aca="false">IF($D29=0,0,$E29/$D29)</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29)</f>
+        <v>9</v>
+      </c>
+      <c r="I29" s="0" t="str">
+        <f aca="false">IF(AND($D29&gt;0,$H29=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B30" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
+        <v>6</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <f aca="false">IF($D30=0,0,$E30/$D30)</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30)</f>
+        <v>11</v>
+      </c>
+      <c r="I30" s="0" t="str">
+        <f aca="false">IF(AND($D30&gt;0,$H30=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B31" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>11</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
+        <v>2</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
+        <v>8</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <f aca="false">IF($D31=0,0,$E31/$D31)</f>
+        <v>0.181818181818182</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31)</f>
+        <v>10</v>
+      </c>
+      <c r="I31" s="0" t="str">
+        <f aca="false">IF(AND($D31&gt;0,$H31=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B32" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>8</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
+        <v>2</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
+        <v>6</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <f aca="false">IF($D32=0,0,$E32/$D32)</f>
+        <v>0.25</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32)</f>
+        <v>20</v>
+      </c>
+      <c r="I32" s="0" t="str">
+        <f aca="false">IF(AND($D32&gt;0,$H32=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B33" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
+        <v>4</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
+        <v>5</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <f aca="false">IF($D33=0,0,$E33/$D33)</f>
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33)</f>
+        <v>20</v>
+      </c>
+      <c r="I33" s="0" t="str">
+        <f aca="false">IF(AND($D33&gt;0,$H33=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B34" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
+        <v>1</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
+        <v>5</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <f aca="false">IF($D34=0,0,$E34/$D34)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34)</f>
+        <v>18</v>
+      </c>
+      <c r="I34" s="0" t="str">
+        <f aca="false">IF(AND($D34&gt;0,$H34=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B35" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
+        <v>1</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
+        <v>5</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <f aca="false">IF($D35=0,0,$E35/$D35)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35)</f>
+        <v>6</v>
+      </c>
+      <c r="I35" s="0" t="str">
+        <f aca="false">IF(AND($D35&gt;0,$H35=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B36" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
+        <v>2</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
+        <v>4</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <f aca="false">IF($D36=0,0,$E36/$D36)</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36)</f>
+        <v>17</v>
+      </c>
+      <c r="I36" s="0" t="str">
+        <f aca="false">IF(AND($D36&gt;0,$H36=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B37" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>13</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
+        <v>6</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
+        <v>7</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <f aca="false">IF($D37=0,0,$E37/$D37)</f>
+        <v>0.461538461538462</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37)</f>
+        <v>26</v>
+      </c>
+      <c r="I37" s="0" t="str">
+        <f aca="false">IF(AND($D37&gt;0,$H37=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B38" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>21</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
+        <v>11</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
+        <v>10</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <f aca="false">IF($D38=0,0,$E38/$D38)</f>
+        <v>0.523809523809524</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38)</f>
+        <v>40</v>
+      </c>
+      <c r="I38" s="0" t="str">
+        <f aca="false">IF(AND($D38&gt;0,$H38=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B39" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <f aca="false">IF($D39=0,0,$E39/$D39)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39)</f>
+        <v>11</v>
+      </c>
+      <c r="I39" s="0" t="str">
+        <f aca="false">IF(AND($D39&gt;0,$H39=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B40" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <f aca="false">IF($D40=0,0,$E40/$D40)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40)</f>
+        <v>20</v>
+      </c>
+      <c r="I40" s="0" t="str">
+        <f aca="false">IF(AND($D40&gt;0,$H40=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B41" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>31</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
+        <v>4</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
+        <v>27</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <f aca="false">IF($D41=0,0,$E41/$D41)</f>
+        <v>0.129032258064516</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41)</f>
+        <v>36</v>
+      </c>
+      <c r="I41" s="0" t="str">
+        <f aca="false">IF(AND($D41&gt;0,$H41=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B42" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
+        <v>7</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <f aca="false">IF($D42=0,0,$E42/$D42)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42)</f>
+        <v>9</v>
+      </c>
+      <c r="I42" s="0" t="str">
+        <f aca="false">IF(AND($D42&gt;0,$H42=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B43" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>10</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
+        <v>10</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <f aca="false">IF($D43=0,0,$E43/$D43)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43)</f>
+        <v>11</v>
+      </c>
+      <c r="I43" s="0" t="str">
+        <f aca="false">IF(AND($D43&gt;0,$H43=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B44" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>11</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
+        <v>2</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
+        <v>8</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <f aca="false">IF($D44=0,0,$E44/$D44)</f>
+        <v>0.181818181818182</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44)</f>
+        <v>10</v>
+      </c>
+      <c r="I44" s="0" t="str">
+        <f aca="false">IF(AND($D44&gt;0,$H44=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B45" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <f aca="false">IF($D45=0,0,$E45/$D45)</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45)</f>
+        <v>20</v>
+      </c>
+      <c r="I45" s="0" t="str">
+        <f aca="false">IF(AND($D45&gt;0,$H45=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B46" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
+        <v>4</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
+        <v>5</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <f aca="false">IF($D46=0,0,$E46/$D46)</f>
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46)</f>
+        <v>20</v>
+      </c>
+      <c r="I46" s="0" t="str">
+        <f aca="false">IF(AND($D46&gt;0,$H46=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B47" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
+        <v>1</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
+        <v>6</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <f aca="false">IF($D47=0,0,$E47/$D47)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47)</f>
+        <v>18</v>
+      </c>
+      <c r="I47" s="0" t="str">
+        <f aca="false">IF(AND($D47&gt;0,$H47=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B48" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
+        <v>1</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
+        <v>5</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <f aca="false">IF($D48=0,0,$E48/$D48)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48)</f>
+        <v>6</v>
+      </c>
+      <c r="I48" s="0" t="str">
+        <f aca="false">IF(AND($D48&gt;0,$H48=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B49" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
+        <v>2</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
+        <v>5</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <f aca="false">IF($D49=0,0,$E49/$D49)</f>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49)</f>
+        <v>17</v>
+      </c>
+      <c r="I49" s="0" t="str">
+        <f aca="false">IF(AND($D49&gt;0,$H49=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B50" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>11</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
+        <v>6</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
+        <v>5</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <f aca="false">IF($D50=0,0,$E50/$D50)</f>
+        <v>0.545454545454545</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50)</f>
+        <v>26</v>
+      </c>
+      <c r="I50" s="0" t="str">
+        <f aca="false">IF(AND($D50&gt;0,$H50=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B51" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>20</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
+        <v>10</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
+        <v>10</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <f aca="false">IF($D51=0,0,$E51/$D51)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51)</f>
+        <v>40</v>
+      </c>
+      <c r="I51" s="0" t="str">
+        <f aca="false">IF(AND($D51&gt;0,$H51=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B52" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <f aca="false">IF($D52=0,0,$E52/$D52)</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52)</f>
+        <v>11</v>
+      </c>
+      <c r="I52" s="0" t="str">
+        <f aca="false">IF(AND($D52&gt;0,$H52=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B53" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <f aca="false">IF($D53=0,0,$E53/$D53)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53)</f>
+        <v>20</v>
+      </c>
+      <c r="I53" s="0" t="str">
+        <f aca="false">IF(AND($D53&gt;0,$H53=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B54" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>27</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
+        <v>4</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
+        <v>23</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <f aca="false">IF($D54=0,0,$E54/$D54)</f>
+        <v>0.148148148148148</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54)</f>
+        <v>36</v>
+      </c>
+      <c r="I54" s="0" t="str">
+        <f aca="false">IF(AND($D54&gt;0,$H54=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B55" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
+        <v>7</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <f aca="false">IF($D55=0,0,$E55/$D55)</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55)</f>
+        <v>9</v>
+      </c>
+      <c r="I55" s="0" t="str">
+        <f aca="false">IF(AND($D55&gt;0,$H55=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B56" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>8</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
+        <v>8</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <f aca="false">IF($D56=0,0,$E56/$D56)</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56)</f>
+        <v>11</v>
+      </c>
+      <c r="I56" s="0" t="str">
+        <f aca="false">IF(AND($D56&gt;0,$H56=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B57" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
+        <v>2</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
+        <v>7</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <f aca="false">IF($D57=0,0,$E57/$D57)</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57)</f>
+        <v>10</v>
+      </c>
+      <c r="I57" s="0" t="str">
+        <f aca="false">IF(AND($D57&gt;0,$H57=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B58" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>5</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
+        <v>2</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
+        <v>3</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <f aca="false">IF($D58=0,0,$E58/$D58)</f>
+        <v>0.4</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58)</f>
+        <v>20</v>
+      </c>
+      <c r="I58" s="0" t="str">
+        <f aca="false">IF(AND($D58&gt;0,$H58=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B59" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
+        <v>4</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
+        <v>5</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <f aca="false">IF($D59=0,0,$E59/$D59)</f>
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59)</f>
+        <v>20</v>
+      </c>
+      <c r="I59" s="0" t="str">
+        <f aca="false">IF(AND($D59&gt;0,$H59=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B60" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
+        <v>1</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
+        <v>5</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <f aca="false">IF($D60=0,0,$E60/$D60)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60)</f>
+        <v>18</v>
+      </c>
+      <c r="I60" s="0" t="str">
+        <f aca="false">IF(AND($D60&gt;0,$H60=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B61" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
+        <v>1</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
+        <v>5</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <f aca="false">IF($D61=0,0,$E61/$D61)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61)</f>
+        <v>6</v>
+      </c>
+      <c r="I61" s="0" t="str">
+        <f aca="false">IF(AND($D61&gt;0,$H61=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B62" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
+        <v>2</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
+        <v>5</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <f aca="false">IF($D62=0,0,$E62/$D62)</f>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62)</f>
+        <v>17</v>
+      </c>
+      <c r="I62" s="0" t="str">
+        <f aca="false">IF(AND($D62&gt;0,$H62=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B63" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>15</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
+        <v>6</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
+        <v>9</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <f aca="false">IF($D63=0,0,$E63/$D63)</f>
+        <v>0.4</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63)</f>
+        <v>26</v>
+      </c>
+      <c r="I63" s="0" t="str">
+        <f aca="false">IF(AND($D63&gt;0,$H63=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B64" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>20</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
+        <v>10</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
+        <v>10</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <f aca="false">IF($D64=0,0,$E64/$D64)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64)</f>
+        <v>40</v>
+      </c>
+      <c r="I64" s="0" t="str">
+        <f aca="false">IF(AND($D64&gt;0,$H64=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B65" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
+        <v>0</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <f aca="false">IF($D65=0,0,$E65/$D65)</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65)</f>
+        <v>11</v>
+      </c>
+      <c r="I65" s="0" t="str">
+        <f aca="false">IF(AND($D65&gt;0,$H65=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B66" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <f aca="false">IF($D66=0,0,$E66/$D66)</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66)</f>
+        <v>20</v>
+      </c>
+      <c r="I66" s="0" t="str">
+        <f aca="false">IF(AND($D66&gt;0,$H66=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B67" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>25</v>
+      </c>
+      <c r="E67" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
+        <v>4</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
+        <v>21</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <f aca="false">IF($D67=0,0,$E67/$D67)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H67" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67)</f>
+        <v>36</v>
+      </c>
+      <c r="I67" s="0" t="str">
+        <f aca="false">IF(AND($D67&gt;0,$H67=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B68" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E68" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
+        <v>7</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <f aca="false">IF($D68=0,0,$E68/$D68)</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68)</f>
+        <v>9</v>
+      </c>
+      <c r="I68" s="0" t="str">
+        <f aca="false">IF(AND($D68&gt;0,$H68=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B69" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E69" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
+        <v>7</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <f aca="false">IF($D69=0,0,$E69/$D69)</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69)</f>
+        <v>11</v>
+      </c>
+      <c r="I69" s="0" t="str">
+        <f aca="false">IF(AND($D69&gt;0,$H69=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B70" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>11</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
+        <v>2</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
+        <v>8</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <f aca="false">IF($D70=0,0,$E70/$D70)</f>
+        <v>0.181818181818182</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70)</f>
+        <v>10</v>
+      </c>
+      <c r="I70" s="0" t="str">
+        <f aca="false">IF(AND($D70&gt;0,$H70=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B71" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
+        <v>2</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
+        <v>4</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <f aca="false">IF($D71=0,0,$E71/$D71)</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H71" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71)</f>
+        <v>20</v>
+      </c>
+      <c r="I71" s="0" t="str">
+        <f aca="false">IF(AND($D71&gt;0,$H71=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B72" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
+        <v>5</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
+        <v>5</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <f aca="false">IF($D72=0,0,$E72/$D72)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72)</f>
+        <v>20</v>
+      </c>
+      <c r="I72" s="0" t="str">
+        <f aca="false">IF(AND($D72&gt;0,$H72=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B73" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
+        <v>1</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
+        <v>6</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <f aca="false">IF($D73=0,0,$E73/$D73)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73)</f>
+        <v>18</v>
+      </c>
+      <c r="I73" s="0" t="str">
+        <f aca="false">IF(AND($D73&gt;0,$H73=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B74" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>5</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
+        <v>1</v>
+      </c>
+      <c r="F74" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
+        <v>4</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <f aca="false">IF($D74=0,0,$E74/$D74)</f>
+        <v>0.2</v>
+      </c>
+      <c r="H74" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74)</f>
+        <v>6</v>
+      </c>
+      <c r="I74" s="0" t="str">
+        <f aca="false">IF(AND($D74&gt;0,$H74=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B75" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E75" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
+        <v>2</v>
+      </c>
+      <c r="F75" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
+        <v>5</v>
+      </c>
+      <c r="G75" s="0" t="n">
+        <f aca="false">IF($D75=0,0,$E75/$D75)</f>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="H75" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75)</f>
+        <v>17</v>
+      </c>
+      <c r="I75" s="0" t="str">
+        <f aca="false">IF(AND($D75&gt;0,$H75=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B76" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>13</v>
+      </c>
+      <c r="E76" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
+        <v>6</v>
+      </c>
+      <c r="F76" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
+        <v>7</v>
+      </c>
+      <c r="G76" s="0" t="n">
+        <f aca="false">IF($D76=0,0,$E76/$D76)</f>
+        <v>0.461538461538462</v>
+      </c>
+      <c r="H76" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76)</f>
+        <v>26</v>
+      </c>
+      <c r="I76" s="0" t="str">
+        <f aca="false">IF(AND($D76&gt;0,$H76=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B77" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>22</v>
+      </c>
+      <c r="E77" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
+        <v>11</v>
+      </c>
+      <c r="F77" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
+        <v>11</v>
+      </c>
+      <c r="G77" s="0" t="n">
+        <f aca="false">IF($D77=0,0,$E77/$D77)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H77" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77)</f>
+        <v>40</v>
+      </c>
+      <c r="I77" s="0" t="str">
+        <f aca="false">IF(AND($D77&gt;0,$H77=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B78" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E78" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
+        <v>0</v>
+      </c>
+      <c r="G78" s="0" t="n">
+        <f aca="false">IF($D78=0,0,$E78/$D78)</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78)</f>
+        <v>11</v>
+      </c>
+      <c r="I78" s="0" t="str">
+        <f aca="false">IF(AND($D78&gt;0,$H78=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="13" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B79" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E79" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
+        <v>0</v>
+      </c>
+      <c r="G79" s="0" t="n">
+        <f aca="false">IF($D79=0,0,$E79/$D79)</f>
+        <v>0</v>
+      </c>
+      <c r="H79" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79)</f>
+        <v>20</v>
+      </c>
+      <c r="I79" s="0" t="str">
+        <f aca="false">IF(AND($D79&gt;0,$H79=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/party-comparison-updated-v83.xlsx
+++ b/party-comparison-updated-v83.xlsx
@@ -114,6 +114,26 @@
           </rPr>
           <t xml:space="preserve">are new parties not previously in the sheet.
 Rounding rule (user 2026-07-21): round poll average to nearest integer; any party at 3 seats or fewer set to 0.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ממוצע </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5 מדגמי הטלוויזיה (27.10.2026) מתוך סקרים לפי ערוץ - ללא ערוץ 16, שפרסם רק מדגם ראשון. מפלגה שאינה במדגמים = 0.</t>
         </r>
       </text>
     </comment>
@@ -482,7 +502,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="1852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="1847">
   <si>
     <t xml:space="preserve">מפלגה</t>
   </si>
@@ -7242,25 +7262,7 @@
     <t xml:space="preserve">מספר משיבים</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">חדשות </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
+    <t xml:space="preserve">חדשות 12</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-27</t>
@@ -7269,25 +7271,7 @@
     <t xml:space="preserve">מנו גבע</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">חדשות </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
+    <t xml:space="preserve">חדשות 13</t>
   </si>
   <si>
     <t xml:space="preserve">המדד</t>
@@ -7299,25 +7283,7 @@
     <t xml:space="preserve">דודי חסיד</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ערוץ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14</t>
-    </r>
+    <t xml:space="preserve">ערוץ 14</t>
   </si>
   <si>
     <t xml:space="preserve">שלמה פילבר</t>
@@ -7329,25 +7295,7 @@
     <t xml:space="preserve">צוריאל שרון</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ערוץ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
+    <t xml:space="preserve">ערוץ 16</t>
   </si>
   <si>
     <t xml:space="preserve">יצחק כ״ץ</t>
@@ -7356,236 +7304,10 @@
     <t xml:space="preserve">מנדטים</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">מועמדים ידועים </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">סה</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">כ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">מועמדים ידועים (סה"כ)</t>
   </si>
   <si>
     <t xml:space="preserve">הערה</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ש</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ס</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">רע</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">מ</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ביחד </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">בנט</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">לפיד</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ישר</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">המילואימניקים</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">הכלכלית</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -7760,7 +7482,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7810,10 +7532,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -42372,15 +42090,16 @@
         <v>1474</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>21.3</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A2,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>27.8</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">ROUND(B2,0)</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="n">
         <f aca="false">IF(C2&lt;=3,0,C2)</f>
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42388,7 +42107,8 @@
         <v>1488</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>21.4</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A3,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>20.8</v>
       </c>
       <c r="C3" s="1" t="n">
         <f aca="false">ROUND(B3,0)</f>
@@ -42404,7 +42124,8 @@
         <v>1489</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>13.2</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A4,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>12.8</v>
       </c>
       <c r="C4" s="1" t="n">
         <f aca="false">ROUND(B4,0)</f>
@@ -42420,7 +42141,8 @@
         <v>1477</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>9.2</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A5,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">ROUND(B5,0)</f>
@@ -42436,15 +42158,16 @@
         <v>1490</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>7.4</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A6,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>5.4</v>
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">ROUND(B6,0)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1" t="n">
         <f aca="false">IF(C6&lt;=3,0,C6)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42452,15 +42175,16 @@
         <v>1479</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>7.9</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A7,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>7.4</v>
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">ROUND(B7,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="n">
         <f aca="false">IF(C7&lt;=3,0,C7)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42468,15 +42192,16 @@
         <v>1481</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7.7</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A8,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>6.4</v>
       </c>
       <c r="C8" s="1" t="n">
         <f aca="false">ROUND(B8,0)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="n">
         <f aca="false">IF(C8&lt;=3,0,C8)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42484,15 +42209,16 @@
         <v>1480</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>7.3</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A9,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>6.4</v>
       </c>
       <c r="C9" s="1" t="n">
         <f aca="false">ROUND(B9,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1" t="n">
         <f aca="false">IF(C9&lt;=3,0,C9)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42500,15 +42226,16 @@
         <v>1491</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>8.6</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A10,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>10.8</v>
       </c>
       <c r="C10" s="1" t="n">
         <f aca="false">ROUND(B10,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="n">
         <f aca="false">IF(C10&lt;=3,0,C10)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42516,15 +42243,16 @@
         <v>1484</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>6.8</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A11,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>6.2</v>
       </c>
       <c r="C11" s="1" t="n">
         <f aca="false">ROUND(B11,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="n">
         <f aca="false">IF(C11&lt;=3,0,C11)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42532,15 +42260,16 @@
         <v>1482</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>5.4</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A12,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="n">
         <f aca="false">ROUND(B12,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="n">
         <f aca="false">IF(C12&lt;=3,0,C12)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42548,11 +42277,12 @@
         <v>1492</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.9</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A13,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>0</v>
       </c>
       <c r="C13" s="1" t="n">
         <f aca="false">ROUND(B13,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1" t="n">
         <f aca="false">IF(C13&lt;=3,0,C13)</f>
@@ -42564,11 +42294,12 @@
         <v>1493</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1.6</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A14,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="n">
         <f aca="false">ROUND(B14,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="n">
         <f aca="false">IF(C14&lt;=3,0,C14)</f>
@@ -42580,11 +42311,12 @@
         <v>1494</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>1.2</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A15,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="n">
         <f aca="false">ROUND(B15,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="n">
         <f aca="false">IF(C15&lt;=3,0,C15)</f>
@@ -42596,11 +42328,12 @@
         <v>1495</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>3.1</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A16,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="n">
         <f aca="false">ROUND(B16,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1" t="n">
         <f aca="false">IF(C16&lt;=3,0,C16)</f>
@@ -42612,15 +42345,16 @@
         <v>1496</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>3.6</v>
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A17,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <v>0</v>
       </c>
       <c r="C17" s="1" t="n">
         <f aca="false">ROUND(B17,0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1" t="n">
         <f aca="false">IF(C17&lt;=3,0,C17)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42628,6 +42362,7 @@
         <v>1497</v>
       </c>
       <c r="B18" s="1" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A18,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
         <v>0</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -42644,6 +42379,7 @@
         <v>1498</v>
       </c>
       <c r="B19" s="1" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A19,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
         <v>0</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -46998,15 +46734,15 @@
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A2,'סקר 2026'!$A:$A,0))</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A2,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A2,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B2)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="n">
         <f aca="false">IF(B2=0,0,C2/B2)</f>
@@ -47134,7 +46870,7 @@
       </c>
       <c r="B6" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A6,'סקר 2026'!$A:$A,0))</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B6)</f>
@@ -47142,11 +46878,11 @@
       </c>
       <c r="D6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B6)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">IF(B6=0,0,C6/B6)</f>
-        <v>0.285714285714286</v>
+        <v>0.4</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>1816</v>
@@ -47168,7 +46904,7 @@
       </c>
       <c r="B7" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A7,'סקר 2026'!$A:$A,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A7,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B7)</f>
@@ -47176,7 +46912,7 @@
       </c>
       <c r="D7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A7,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B7)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">IF(B7=0,0,C7/B7)</f>
@@ -47202,7 +46938,7 @@
       </c>
       <c r="B8" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A8,'סקר 2026'!$A:$A,0))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A8,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B8)</f>
@@ -47210,11 +46946,11 @@
       </c>
       <c r="D8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A8,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B8)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="n">
         <f aca="false">IF(B8=0,0,C8/B8)</f>
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>1818</v>
@@ -47236,7 +46972,7 @@
       </c>
       <c r="B9" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A9,'סקר 2026'!$A:$A,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A9,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B9)</f>
@@ -47244,7 +46980,7 @@
       </c>
       <c r="D9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A9,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B9)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1" t="n">
         <f aca="false">IF(B9=0,0,C9/B9)</f>
@@ -47270,7 +47006,7 @@
       </c>
       <c r="B10" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A10,'סקר 2026'!$A:$A,0))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A10,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B10)</f>
@@ -47278,11 +47014,11 @@
       </c>
       <c r="D10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A10,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B10)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="n">
         <f aca="false">IF(B10=0,0,C10/B10)</f>
-        <v>0.222222222222222</v>
+        <v>0.181818181818182</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>1820</v>
@@ -47304,7 +47040,7 @@
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A11,'סקר 2026'!$A:$A,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A11,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B11)</f>
@@ -47312,11 +47048,11 @@
       </c>
       <c r="D11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A11,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B11)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="n">
         <f aca="false">IF(B11=0,0,C11/B11)</f>
-        <v>0.142857142857143</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>1821</v>
@@ -47338,7 +47074,7 @@
       </c>
       <c r="B12" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A12,'סקר 2026'!$A:$A,0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A12,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B12)</f>
@@ -47346,11 +47082,11 @@
       </c>
       <c r="D12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A12,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B12)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="n">
         <f aca="false">IF(B12=0,0,C12/B12)</f>
-        <v>0.2</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>1822</v>
@@ -47406,19 +47142,19 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A14,'סקר 2026'!$A:$A,0))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A14,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B14)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A14,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B14)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="n">
         <f aca="false">IF(B14=0,0,C14/B14)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>1824</v>
@@ -47482,7 +47218,7 @@
       </c>
       <c r="D16" s="1" t="n">
         <f aca="false">SUM(D2:D14)</f>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1" t="n">
         <f aca="false">IF(B16=0,0,C16/B16)</f>
@@ -47578,320 +47314,320 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="3" t="s">
         <v>1833</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" s="0" t="n">
+      <c r="Q2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="3" t="s">
         <v>1835</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="Q3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="3" t="s">
         <v>1837</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="3" t="s">
         <v>1839</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="3" t="s">
         <v>1841</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="3" t="s">
         <v>1843</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -47915,2839 +47651,2839 @@
   <dimension ref="A1:I79"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>1827</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="3" t="s">
         <v>1828</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="3" t="s">
         <v>1844</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="3" t="s">
         <v>1472</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="3" t="s">
         <v>1473</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="3" t="s">
         <v>1807</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="3" t="s">
         <v>1845</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="3" t="s">
         <v>1846</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B2" s="0" t="str">
+      <c r="B2" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
         <v>23</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <f aca="false">IF($D2=0,0,$E2/$D2)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2)</f>
         <v>36</v>
       </c>
-      <c r="I2" s="0" t="str">
+      <c r="I2" s="1" t="str">
         <f aca="false">IF(AND($D2&gt;0,$H2=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B3" s="0" t="str">
+      <c r="B3" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
         <v>6</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <f aca="false">IF($D3=0,0,$E3/$D3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3)</f>
         <v>9</v>
       </c>
-      <c r="I3" s="0" t="str">
+      <c r="I3" s="1" t="str">
         <f aca="false">IF(AND($D3&gt;0,$H3=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B4" s="0" t="str">
+      <c r="B4" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
         <v>7</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <f aca="false">IF($D4=0,0,$E4/$D4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4)</f>
         <v>11</v>
       </c>
-      <c r="I4" s="0" t="str">
+      <c r="I4" s="1" t="str">
         <f aca="false">IF(AND($D4&gt;0,$H4=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B5" s="0" t="str">
+      <c r="B5" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>12</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
         <v>8</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <f aca="false">IF($D5=0,0,$E5/$D5)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5)</f>
         <v>10</v>
       </c>
-      <c r="I5" s="0" t="str">
+      <c r="I5" s="1" t="str">
         <f aca="false">IF(AND($D5&gt;0,$H5=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B6" s="0" t="str">
+      <c r="B6" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
         <v>2</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
         <v>5</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <f aca="false">IF($D6=0,0,$E6/$D6)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6)</f>
         <v>20</v>
       </c>
-      <c r="I6" s="0" t="str">
+      <c r="I6" s="1" t="str">
         <f aca="false">IF(AND($D6&gt;0,$H6=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B7" s="0" t="str">
+      <c r="B7" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
         <v>4</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
         <v>5</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <f aca="false">IF($D7=0,0,$E7/$D7)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7)</f>
         <v>20</v>
       </c>
-      <c r="I7" s="0" t="str">
+      <c r="I7" s="1" t="str">
         <f aca="false">IF(AND($D7&gt;0,$H7=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B8" s="0" t="str">
+      <c r="B8" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
         <v>5</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <f aca="false">IF($D8=0,0,$E8/$D8)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8)</f>
         <v>18</v>
       </c>
-      <c r="I8" s="0" t="str">
+      <c r="I8" s="1" t="str">
         <f aca="false">IF(AND($D8&gt;0,$H8=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B9" s="0" t="str">
+      <c r="B9" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
         <v>1</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
         <v>5</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <f aca="false">IF($D9=0,0,$E9/$D9)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9)</f>
         <v>6</v>
       </c>
-      <c r="I9" s="0" t="str">
+      <c r="I9" s="1" t="str">
         <f aca="false">IF(AND($D9&gt;0,$H9=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B10" s="0" t="str">
+      <c r="B10" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
         <v>4</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <f aca="false">IF($D10=0,0,$E10/$D10)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10)</f>
         <v>17</v>
       </c>
-      <c r="I10" s="0" t="str">
+      <c r="I10" s="1" t="str">
         <f aca="false">IF(AND($D10&gt;0,$H10=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B11" s="0" t="str">
+      <c r="B11" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>12</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
         <v>6</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <f aca="false">IF($D11=0,0,$E11/$D11)</f>
         <v>0.5</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11)</f>
         <v>26</v>
       </c>
-      <c r="I11" s="0" t="str">
+      <c r="I11" s="1" t="str">
         <f aca="false">IF(AND($D11&gt;0,$H11=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B12" s="0" t="str">
+      <c r="B12" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
         <v>11</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
         <v>10</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <f aca="false">IF($D12=0,0,$E12/$D12)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12)</f>
         <v>40</v>
       </c>
-      <c r="I12" s="0" t="str">
+      <c r="I12" s="1" t="str">
         <f aca="false">IF(AND($D12&gt;0,$H12=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B13" s="0" t="str">
+      <c r="B13" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <f aca="false">IF($D13=0,0,$E13/$D13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13)</f>
         <v>11</v>
       </c>
-      <c r="I13" s="0" t="str">
+      <c r="I13" s="1" t="str">
         <f aca="false">IF(AND($D13&gt;0,$H13=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B14" s="0" t="str">
+      <c r="B14" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <f aca="false">IF($D14=0,0,$E14/$D14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14)</f>
         <v>20</v>
       </c>
-      <c r="I14" s="0" t="str">
+      <c r="I14" s="1" t="str">
         <f aca="false">IF(AND($D14&gt;0,$H14=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B15" s="0" t="str">
+      <c r="B15" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
         <v>4</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
         <v>23</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <f aca="false">IF($D15=0,0,$E15/$D15)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15)</f>
         <v>36</v>
       </c>
-      <c r="I15" s="0" t="str">
+      <c r="I15" s="1" t="str">
         <f aca="false">IF(AND($D15&gt;0,$H15=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B16" s="0" t="str">
+      <c r="B16" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
         <v>6</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <f aca="false">IF($D16=0,0,$E16/$D16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16)</f>
         <v>9</v>
       </c>
-      <c r="I16" s="0" t="str">
+      <c r="I16" s="1" t="str">
         <f aca="false">IF(AND($D16&gt;0,$H16=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B17" s="0" t="str">
+      <c r="B17" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
         <v>6</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <f aca="false">IF($D17=0,0,$E17/$D17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17)</f>
         <v>11</v>
       </c>
-      <c r="I17" s="0" t="str">
+      <c r="I17" s="1" t="str">
         <f aca="false">IF(AND($D17&gt;0,$H17=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B18" s="0" t="str">
+      <c r="B18" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
         <v>2</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
         <v>8</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <f aca="false">IF($D18=0,0,$E18/$D18)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18)</f>
         <v>10</v>
       </c>
-      <c r="I18" s="0" t="str">
+      <c r="I18" s="1" t="str">
         <f aca="false">IF(AND($D18&gt;0,$H18=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B19" s="0" t="str">
+      <c r="B19" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
         <v>2</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
         <v>5</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <f aca="false">IF($D19=0,0,$E19/$D19)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19)</f>
         <v>20</v>
       </c>
-      <c r="I19" s="0" t="str">
+      <c r="I19" s="1" t="str">
         <f aca="false">IF(AND($D19&gt;0,$H19=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B20" s="0" t="str">
+      <c r="B20" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
         <v>4</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
         <v>5</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <f aca="false">IF($D20=0,0,$E20/$D20)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20)</f>
         <v>20</v>
       </c>
-      <c r="I20" s="0" t="str">
+      <c r="I20" s="1" t="str">
         <f aca="false">IF(AND($D20&gt;0,$H20=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B21" s="0" t="str">
+      <c r="B21" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <f aca="false">IF($D21=0,0,$E21/$D21)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21)</f>
         <v>18</v>
       </c>
-      <c r="I21" s="0" t="str">
+      <c r="I21" s="1" t="str">
         <f aca="false">IF(AND($D21&gt;0,$H21=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B22" s="0" t="str">
+      <c r="B22" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="C22" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
         <v>1</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
         <v>5</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="1" t="n">
         <f aca="false">IF($D22=0,0,$E22/$D22)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22)</f>
         <v>6</v>
       </c>
-      <c r="I22" s="0" t="str">
+      <c r="I22" s="1" t="str">
         <f aca="false">IF(AND($D22&gt;0,$H22=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B23" s="0" t="str">
+      <c r="B23" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
         <v>4</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="1" t="n">
         <f aca="false">IF($D23=0,0,$E23/$D23)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23)</f>
         <v>17</v>
       </c>
-      <c r="I23" s="0" t="str">
+      <c r="I23" s="1" t="str">
         <f aca="false">IF(AND($D23&gt;0,$H23=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B24" s="0" t="str">
+      <c r="B24" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D24" s="0" t="n">
+      <c r="C24" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D24" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
         <v>6</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
         <v>7</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="1" t="n">
         <f aca="false">IF($D24=0,0,$E24/$D24)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24)</f>
         <v>26</v>
       </c>
-      <c r="I24" s="0" t="str">
+      <c r="I24" s="1" t="str">
         <f aca="false">IF(AND($D24&gt;0,$H24=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B25" s="0" t="str">
+      <c r="B25" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D25" s="0" t="n">
+      <c r="C25" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D25" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>22</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
         <v>11</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
         <v>11</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="1" t="n">
         <f aca="false">IF($D25=0,0,$E25/$D25)</f>
         <v>0.5</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25)</f>
         <v>40</v>
       </c>
-      <c r="I25" s="0" t="str">
+      <c r="I25" s="1" t="str">
         <f aca="false">IF(AND($D25&gt;0,$H25=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B26" s="0" t="str">
+      <c r="B26" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="1" t="n">
         <f aca="false">IF($D26=0,0,$E26/$D26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26)</f>
         <v>11</v>
       </c>
-      <c r="I26" s="0" t="str">
+      <c r="I26" s="1" t="str">
         <f aca="false">IF(AND($D26&gt;0,$H26=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>1834</v>
       </c>
-      <c r="B27" s="0" t="str">
+      <c r="B27" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D27" s="0" t="n">
+      <c r="C27" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D27" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="1" t="n">
         <f aca="false">IF($D27=0,0,$E27/$D27)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27)</f>
         <v>20</v>
       </c>
-      <c r="I27" s="0" t="str">
+      <c r="I27" s="1" t="str">
         <f aca="false">IF(AND($D27&gt;0,$H27=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B28" s="0" t="str">
+      <c r="B28" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
         <v>23</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <f aca="false">IF($D28=0,0,$E28/$D28)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28)</f>
         <v>36</v>
       </c>
-      <c r="I28" s="0" t="str">
+      <c r="I28" s="1" t="str">
         <f aca="false">IF(AND($D28&gt;0,$H28=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B29" s="0" t="str">
+      <c r="B29" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
         <v>6</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="1" t="n">
         <f aca="false">IF($D29=0,0,$E29/$D29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29)</f>
         <v>9</v>
       </c>
-      <c r="I29" s="0" t="str">
+      <c r="I29" s="1" t="str">
         <f aca="false">IF(AND($D29&gt;0,$H29=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B30" s="0" t="str">
+      <c r="B30" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D30" s="0" t="n">
+      <c r="C30" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D30" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
         <v>6</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="1" t="n">
         <f aca="false">IF($D30=0,0,$E30/$D30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30)</f>
         <v>11</v>
       </c>
-      <c r="I30" s="0" t="str">
+      <c r="I30" s="1" t="str">
         <f aca="false">IF(AND($D30&gt;0,$H30=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B31" s="0" t="str">
+      <c r="B31" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
         <v>2</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
         <v>8</v>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="G31" s="1" t="n">
         <f aca="false">IF($D31=0,0,$E31/$D31)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31)</f>
         <v>10</v>
       </c>
-      <c r="I31" s="0" t="str">
+      <c r="I31" s="1" t="str">
         <f aca="false">IF(AND($D31&gt;0,$H31=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B32" s="0" t="str">
+      <c r="B32" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>8</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
         <v>2</v>
       </c>
-      <c r="F32" s="0" t="n">
+      <c r="F32" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
         <v>6</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32" s="1" t="n">
         <f aca="false">IF($D32=0,0,$E32/$D32)</f>
         <v>0.25</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32)</f>
         <v>20</v>
       </c>
-      <c r="I32" s="0" t="str">
+      <c r="I32" s="1" t="str">
         <f aca="false">IF(AND($D32&gt;0,$H32=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B33" s="0" t="str">
+      <c r="B33" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
         <v>4</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
         <v>5</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="1" t="n">
         <f aca="false">IF($D33=0,0,$E33/$D33)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33)</f>
         <v>20</v>
       </c>
-      <c r="I33" s="0" t="str">
+      <c r="I33" s="1" t="str">
         <f aca="false">IF(AND($D33&gt;0,$H33=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B34" s="0" t="str">
+      <c r="B34" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
         <v>5</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <f aca="false">IF($D34=0,0,$E34/$D34)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34)</f>
         <v>18</v>
       </c>
-      <c r="I34" s="0" t="str">
+      <c r="I34" s="1" t="str">
         <f aca="false">IF(AND($D34&gt;0,$H34=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B35" s="0" t="str">
+      <c r="B35" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D35" s="0" t="n">
+      <c r="C35" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
         <v>1</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
         <v>5</v>
       </c>
-      <c r="G35" s="0" t="n">
+      <c r="G35" s="1" t="n">
         <f aca="false">IF($D35=0,0,$E35/$D35)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35)</f>
         <v>6</v>
       </c>
-      <c r="I35" s="0" t="str">
+      <c r="I35" s="1" t="str">
         <f aca="false">IF(AND($D35&gt;0,$H35=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B36" s="0" t="str">
+      <c r="B36" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
         <v>2</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
         <v>4</v>
       </c>
-      <c r="G36" s="0" t="n">
+      <c r="G36" s="1" t="n">
         <f aca="false">IF($D36=0,0,$E36/$D36)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36)</f>
         <v>17</v>
       </c>
-      <c r="I36" s="0" t="str">
+      <c r="I36" s="1" t="str">
         <f aca="false">IF(AND($D36&gt;0,$H36=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B37" s="0" t="str">
+      <c r="B37" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D37" s="0" t="n">
+      <c r="C37" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D37" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
         <v>6</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
         <v>7</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="1" t="n">
         <f aca="false">IF($D37=0,0,$E37/$D37)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37)</f>
         <v>26</v>
       </c>
-      <c r="I37" s="0" t="str">
+      <c r="I37" s="1" t="str">
         <f aca="false">IF(AND($D37&gt;0,$H37=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B38" s="0" t="str">
+      <c r="B38" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D38" s="0" t="n">
+      <c r="C38" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D38" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
         <v>11</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
         <v>10</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="1" t="n">
         <f aca="false">IF($D38=0,0,$E38/$D38)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38)</f>
         <v>40</v>
       </c>
-      <c r="I38" s="0" t="str">
+      <c r="I38" s="1" t="str">
         <f aca="false">IF(AND($D38&gt;0,$H38=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B39" s="0" t="str">
+      <c r="B39" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="1" t="n">
         <f aca="false">IF($D39=0,0,$E39/$D39)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39)</f>
         <v>11</v>
       </c>
-      <c r="I39" s="0" t="str">
+      <c r="I39" s="1" t="str">
         <f aca="false">IF(AND($D39&gt;0,$H39=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B40" s="0" t="str">
+      <c r="B40" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D40" s="0" t="n">
+      <c r="C40" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D40" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="1" t="n">
         <f aca="false">IF($D40=0,0,$E40/$D40)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40)</f>
         <v>20</v>
       </c>
-      <c r="I40" s="0" t="str">
+      <c r="I40" s="1" t="str">
         <f aca="false">IF(AND($D40&gt;0,$H40=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B41" s="0" t="str">
+      <c r="B41" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>31</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
         <v>4</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
         <v>27</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G41" s="1" t="n">
         <f aca="false">IF($D41=0,0,$E41/$D41)</f>
         <v>0.129032258064516</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41)</f>
         <v>36</v>
       </c>
-      <c r="I41" s="0" t="str">
+      <c r="I41" s="1" t="str">
         <f aca="false">IF(AND($D41&gt;0,$H41=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B42" s="0" t="str">
+      <c r="B42" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="0" t="n">
+      <c r="F42" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
         <v>7</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="1" t="n">
         <f aca="false">IF($D42=0,0,$E42/$D42)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42)</f>
         <v>9</v>
       </c>
-      <c r="I42" s="0" t="str">
+      <c r="I42" s="1" t="str">
         <f aca="false">IF(AND($D42&gt;0,$H42=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B43" s="0" t="str">
+      <c r="B43" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D43" s="0" t="n">
+      <c r="C43" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D43" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>10</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="0" t="n">
+      <c r="F43" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
         <v>10</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="1" t="n">
         <f aca="false">IF($D43=0,0,$E43/$D43)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43)</f>
         <v>11</v>
       </c>
-      <c r="I43" s="0" t="str">
+      <c r="I43" s="1" t="str">
         <f aca="false">IF(AND($D43&gt;0,$H43=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B44" s="0" t="str">
+      <c r="B44" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
         <v>2</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
         <v>8</v>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="1" t="n">
         <f aca="false">IF($D44=0,0,$E44/$D44)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44)</f>
         <v>10</v>
       </c>
-      <c r="I44" s="0" t="str">
+      <c r="I44" s="1" t="str">
         <f aca="false">IF(AND($D44&gt;0,$H44=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B45" s="0" t="str">
+      <c r="B45" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="0" t="n">
+      <c r="F45" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="1" t="n">
         <f aca="false">IF($D45=0,0,$E45/$D45)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45)</f>
         <v>20</v>
       </c>
-      <c r="I45" s="0" t="str">
+      <c r="I45" s="1" t="str">
         <f aca="false">IF(AND($D45&gt;0,$H45=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B46" s="0" t="str">
+      <c r="B46" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D46" s="0" t="n">
+      <c r="D46" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
         <v>4</v>
       </c>
-      <c r="F46" s="0" t="n">
+      <c r="F46" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
         <v>5</v>
       </c>
-      <c r="G46" s="0" t="n">
+      <c r="G46" s="1" t="n">
         <f aca="false">IF($D46=0,0,$E46/$D46)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46)</f>
         <v>20</v>
       </c>
-      <c r="I46" s="0" t="str">
+      <c r="I46" s="1" t="str">
         <f aca="false">IF(AND($D46&gt;0,$H46=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B47" s="0" t="str">
+      <c r="B47" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D47" s="0" t="n">
+      <c r="D47" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
         <v>1</v>
       </c>
-      <c r="F47" s="0" t="n">
+      <c r="F47" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
         <v>6</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="1" t="n">
         <f aca="false">IF($D47=0,0,$E47/$D47)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47)</f>
         <v>18</v>
       </c>
-      <c r="I47" s="0" t="str">
+      <c r="I47" s="1" t="str">
         <f aca="false">IF(AND($D47&gt;0,$H47=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B48" s="0" t="str">
+      <c r="B48" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D48" s="0" t="n">
+      <c r="C48" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
         <v>1</v>
       </c>
-      <c r="F48" s="0" t="n">
+      <c r="F48" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
         <v>5</v>
       </c>
-      <c r="G48" s="0" t="n">
+      <c r="G48" s="1" t="n">
         <f aca="false">IF($D48=0,0,$E48/$D48)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48)</f>
         <v>6</v>
       </c>
-      <c r="I48" s="0" t="str">
+      <c r="I48" s="1" t="str">
         <f aca="false">IF(AND($D48&gt;0,$H48=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B49" s="0" t="str">
+      <c r="B49" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D49" s="0" t="n">
+      <c r="D49" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
         <v>2</v>
       </c>
-      <c r="F49" s="0" t="n">
+      <c r="F49" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
         <v>5</v>
       </c>
-      <c r="G49" s="0" t="n">
+      <c r="G49" s="1" t="n">
         <f aca="false">IF($D49=0,0,$E49/$D49)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49)</f>
         <v>17</v>
       </c>
-      <c r="I49" s="0" t="str">
+      <c r="I49" s="1" t="str">
         <f aca="false">IF(AND($D49&gt;0,$H49=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B50" s="0" t="str">
+      <c r="B50" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D50" s="0" t="n">
+      <c r="C50" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
         <v>6</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
         <v>5</v>
       </c>
-      <c r="G50" s="0" t="n">
+      <c r="G50" s="1" t="n">
         <f aca="false">IF($D50=0,0,$E50/$D50)</f>
         <v>0.545454545454545</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50)</f>
         <v>26</v>
       </c>
-      <c r="I50" s="0" t="str">
+      <c r="I50" s="1" t="str">
         <f aca="false">IF(AND($D50&gt;0,$H50=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B51" s="0" t="str">
+      <c r="B51" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D51" s="0" t="n">
+      <c r="C51" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>20</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
         <v>10</v>
       </c>
-      <c r="F51" s="0" t="n">
+      <c r="F51" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
         <v>10</v>
       </c>
-      <c r="G51" s="0" t="n">
+      <c r="G51" s="1" t="n">
         <f aca="false">IF($D51=0,0,$E51/$D51)</f>
         <v>0.5</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51)</f>
         <v>40</v>
       </c>
-      <c r="I51" s="0" t="str">
+      <c r="I51" s="1" t="str">
         <f aca="false">IF(AND($D51&gt;0,$H51=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B52" s="0" t="str">
+      <c r="B52" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
         <v>0</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <f aca="false">IF($D52=0,0,$E52/$D52)</f>
         <v>0</v>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52)</f>
         <v>11</v>
       </c>
-      <c r="I52" s="0" t="str">
+      <c r="I52" s="1" t="str">
         <f aca="false">IF(AND($D52&gt;0,$H52=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
         <v>1838</v>
       </c>
-      <c r="B53" s="0" t="str">
+      <c r="B53" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D53" s="0" t="n">
+      <c r="C53" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
         <v>0</v>
       </c>
-      <c r="F53" s="0" t="n">
+      <c r="F53" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
         <v>0</v>
       </c>
-      <c r="G53" s="0" t="n">
+      <c r="G53" s="1" t="n">
         <f aca="false">IF($D53=0,0,$E53/$D53)</f>
         <v>0</v>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53)</f>
         <v>20</v>
       </c>
-      <c r="I53" s="0" t="str">
+      <c r="I53" s="1" t="str">
         <f aca="false">IF(AND($D53&gt;0,$H53=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B54" s="0" t="str">
+      <c r="B54" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
         <v>4</v>
       </c>
-      <c r="F54" s="0" t="n">
+      <c r="F54" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
         <v>23</v>
       </c>
-      <c r="G54" s="0" t="n">
+      <c r="G54" s="1" t="n">
         <f aca="false">IF($D54=0,0,$E54/$D54)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54)</f>
         <v>36</v>
       </c>
-      <c r="I54" s="0" t="str">
+      <c r="I54" s="1" t="str">
         <f aca="false">IF(AND($D54&gt;0,$H54=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B55" s="0" t="str">
+      <c r="B55" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="0" t="n">
+      <c r="F55" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
         <v>7</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <f aca="false">IF($D55=0,0,$E55/$D55)</f>
         <v>0</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55)</f>
         <v>9</v>
       </c>
-      <c r="I55" s="0" t="str">
+      <c r="I55" s="1" t="str">
         <f aca="false">IF(AND($D55&gt;0,$H55=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B56" s="0" t="str">
+      <c r="B56" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D56" s="0" t="n">
+      <c r="C56" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>8</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
         <v>0</v>
       </c>
-      <c r="F56" s="0" t="n">
+      <c r="F56" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
         <v>8</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="1" t="n">
         <f aca="false">IF($D56=0,0,$E56/$D56)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56)</f>
         <v>11</v>
       </c>
-      <c r="I56" s="0" t="str">
+      <c r="I56" s="1" t="str">
         <f aca="false">IF(AND($D56&gt;0,$H56=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B57" s="0" t="str">
+      <c r="B57" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
         <v>2</v>
       </c>
-      <c r="F57" s="0" t="n">
+      <c r="F57" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
         <v>7</v>
       </c>
-      <c r="G57" s="0" t="n">
+      <c r="G57" s="1" t="n">
         <f aca="false">IF($D57=0,0,$E57/$D57)</f>
         <v>0.222222222222222</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57)</f>
         <v>10</v>
       </c>
-      <c r="I57" s="0" t="str">
+      <c r="I57" s="1" t="str">
         <f aca="false">IF(AND($D57&gt;0,$H57=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B58" s="0" t="str">
+      <c r="B58" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D58" s="0" t="n">
+      <c r="D58" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
         <v>2</v>
       </c>
-      <c r="F58" s="0" t="n">
+      <c r="F58" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
         <v>3</v>
       </c>
-      <c r="G58" s="0" t="n">
+      <c r="G58" s="1" t="n">
         <f aca="false">IF($D58=0,0,$E58/$D58)</f>
         <v>0.4</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58)</f>
         <v>20</v>
       </c>
-      <c r="I58" s="0" t="str">
+      <c r="I58" s="1" t="str">
         <f aca="false">IF(AND($D58&gt;0,$H58=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B59" s="0" t="str">
+      <c r="B59" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
         <v>4</v>
       </c>
-      <c r="F59" s="0" t="n">
+      <c r="F59" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
         <v>5</v>
       </c>
-      <c r="G59" s="0" t="n">
+      <c r="G59" s="1" t="n">
         <f aca="false">IF($D59=0,0,$E59/$D59)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59)</f>
         <v>20</v>
       </c>
-      <c r="I59" s="0" t="str">
+      <c r="I59" s="1" t="str">
         <f aca="false">IF(AND($D59&gt;0,$H59=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B60" s="0" t="str">
+      <c r="B60" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
         <v>1</v>
       </c>
-      <c r="F60" s="0" t="n">
+      <c r="F60" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
         <v>5</v>
       </c>
-      <c r="G60" s="0" t="n">
+      <c r="G60" s="1" t="n">
         <f aca="false">IF($D60=0,0,$E60/$D60)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60)</f>
         <v>18</v>
       </c>
-      <c r="I60" s="0" t="str">
+      <c r="I60" s="1" t="str">
         <f aca="false">IF(AND($D60&gt;0,$H60=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B61" s="0" t="str">
+      <c r="B61" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D61" s="0" t="n">
+      <c r="C61" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
         <v>1</v>
       </c>
-      <c r="F61" s="0" t="n">
+      <c r="F61" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
         <v>5</v>
       </c>
-      <c r="G61" s="0" t="n">
+      <c r="G61" s="1" t="n">
         <f aca="false">IF($D61=0,0,$E61/$D61)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61)</f>
         <v>6</v>
       </c>
-      <c r="I61" s="0" t="str">
+      <c r="I61" s="1" t="str">
         <f aca="false">IF(AND($D61&gt;0,$H61=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B62" s="0" t="str">
+      <c r="B62" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
         <v>2</v>
       </c>
-      <c r="F62" s="0" t="n">
+      <c r="F62" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
         <v>5</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="1" t="n">
         <f aca="false">IF($D62=0,0,$E62/$D62)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62)</f>
         <v>17</v>
       </c>
-      <c r="I62" s="0" t="str">
+      <c r="I62" s="1" t="str">
         <f aca="false">IF(AND($D62&gt;0,$H62=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B63" s="0" t="str">
+      <c r="B63" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D63" s="0" t="n">
+      <c r="C63" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D63" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>15</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
         <v>6</v>
       </c>
-      <c r="F63" s="0" t="n">
+      <c r="F63" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
         <v>9</v>
       </c>
-      <c r="G63" s="0" t="n">
+      <c r="G63" s="1" t="n">
         <f aca="false">IF($D63=0,0,$E63/$D63)</f>
         <v>0.4</v>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63)</f>
         <v>26</v>
       </c>
-      <c r="I63" s="0" t="str">
+      <c r="I63" s="1" t="str">
         <f aca="false">IF(AND($D63&gt;0,$H63=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B64" s="0" t="str">
+      <c r="B64" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D64" s="0" t="n">
+      <c r="C64" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D64" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>20</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
         <v>10</v>
       </c>
-      <c r="F64" s="0" t="n">
+      <c r="F64" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
         <v>10</v>
       </c>
-      <c r="G64" s="0" t="n">
+      <c r="G64" s="1" t="n">
         <f aca="false">IF($D64=0,0,$E64/$D64)</f>
         <v>0.5</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64)</f>
         <v>40</v>
       </c>
-      <c r="I64" s="0" t="str">
+      <c r="I64" s="1" t="str">
         <f aca="false">IF(AND($D64&gt;0,$H64=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B65" s="0" t="str">
+      <c r="B65" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
         <v>0</v>
       </c>
-      <c r="F65" s="0" t="n">
+      <c r="F65" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
         <v>0</v>
       </c>
-      <c r="G65" s="0" t="n">
+      <c r="G65" s="1" t="n">
         <f aca="false">IF($D65=0,0,$E65/$D65)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65)</f>
         <v>11</v>
       </c>
-      <c r="I65" s="0" t="str">
+      <c r="I65" s="1" t="str">
         <f aca="false">IF(AND($D65&gt;0,$H65=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>1840</v>
       </c>
-      <c r="B66" s="0" t="str">
+      <c r="B66" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C66" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D66" s="0" t="n">
+      <c r="C66" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D66" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
         <v>0</v>
       </c>
-      <c r="F66" s="0" t="n">
+      <c r="F66" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
         <v>0</v>
       </c>
-      <c r="G66" s="0" t="n">
+      <c r="G66" s="1" t="n">
         <f aca="false">IF($D66=0,0,$E66/$D66)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66)</f>
         <v>20</v>
       </c>
-      <c r="I66" s="0" t="str">
+      <c r="I66" s="1" t="str">
         <f aca="false">IF(AND($D66&gt;0,$H66=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B67" s="0" t="str">
+      <c r="B67" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>25</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
         <v>4</v>
       </c>
-      <c r="F67" s="0" t="n">
+      <c r="F67" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
         <v>21</v>
       </c>
-      <c r="G67" s="0" t="n">
+      <c r="G67" s="1" t="n">
         <f aca="false">IF($D67=0,0,$E67/$D67)</f>
         <v>0.16</v>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67)</f>
         <v>36</v>
       </c>
-      <c r="I67" s="0" t="str">
+      <c r="I67" s="1" t="str">
         <f aca="false">IF(AND($D67&gt;0,$H67=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B68" s="0" t="str">
+      <c r="B68" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D68" s="0" t="n">
+      <c r="D68" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
         <v>0</v>
       </c>
-      <c r="F68" s="0" t="n">
+      <c r="F68" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
         <v>7</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="1" t="n">
         <f aca="false">IF($D68=0,0,$E68/$D68)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68)</f>
         <v>9</v>
       </c>
-      <c r="I68" s="0" t="str">
+      <c r="I68" s="1" t="str">
         <f aca="false">IF(AND($D68&gt;0,$H68=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B69" s="0" t="str">
+      <c r="B69" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D69" s="0" t="n">
+      <c r="C69" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D69" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
         <v>0</v>
       </c>
-      <c r="F69" s="0" t="n">
+      <c r="F69" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
         <v>7</v>
       </c>
-      <c r="G69" s="0" t="n">
+      <c r="G69" s="1" t="n">
         <f aca="false">IF($D69=0,0,$E69/$D69)</f>
         <v>0</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69)</f>
         <v>11</v>
       </c>
-      <c r="I69" s="0" t="str">
+      <c r="I69" s="1" t="str">
         <f aca="false">IF(AND($D69&gt;0,$H69=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B70" s="0" t="str">
+      <c r="B70" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D70" s="0" t="n">
+      <c r="D70" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
         <v>2</v>
       </c>
-      <c r="F70" s="0" t="n">
+      <c r="F70" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
         <v>8</v>
       </c>
-      <c r="G70" s="0" t="n">
+      <c r="G70" s="1" t="n">
         <f aca="false">IF($D70=0,0,$E70/$D70)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70)</f>
         <v>10</v>
       </c>
-      <c r="I70" s="0" t="str">
+      <c r="I70" s="1" t="str">
         <f aca="false">IF(AND($D70&gt;0,$H70=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B71" s="0" t="str">
+      <c r="B71" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
         <v>2</v>
       </c>
-      <c r="F71" s="0" t="n">
+      <c r="F71" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
         <v>4</v>
       </c>
-      <c r="G71" s="0" t="n">
+      <c r="G71" s="1" t="n">
         <f aca="false">IF($D71=0,0,$E71/$D71)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71)</f>
         <v>20</v>
       </c>
-      <c r="I71" s="0" t="str">
+      <c r="I71" s="1" t="str">
         <f aca="false">IF(AND($D71&gt;0,$H71=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B72" s="0" t="str">
+      <c r="B72" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>10</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
         <v>5</v>
       </c>
-      <c r="F72" s="0" t="n">
+      <c r="F72" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
         <v>5</v>
       </c>
-      <c r="G72" s="0" t="n">
+      <c r="G72" s="1" t="n">
         <f aca="false">IF($D72=0,0,$E72/$D72)</f>
         <v>0.5</v>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72)</f>
         <v>20</v>
       </c>
-      <c r="I72" s="0" t="str">
+      <c r="I72" s="1" t="str">
         <f aca="false">IF(AND($D72&gt;0,$H72=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B73" s="0" t="str">
+      <c r="B73" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
         <v>1</v>
       </c>
-      <c r="F73" s="0" t="n">
+      <c r="F73" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
         <v>6</v>
       </c>
-      <c r="G73" s="0" t="n">
+      <c r="G73" s="1" t="n">
         <f aca="false">IF($D73=0,0,$E73/$D73)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73)</f>
         <v>18</v>
       </c>
-      <c r="I73" s="0" t="str">
+      <c r="I73" s="1" t="str">
         <f aca="false">IF(AND($D73&gt;0,$H73=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="13" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B74" s="0" t="str">
+      <c r="B74" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D74" s="0" t="n">
+      <c r="C74" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D74" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
         <v>1</v>
       </c>
-      <c r="F74" s="0" t="n">
+      <c r="F74" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
         <v>4</v>
       </c>
-      <c r="G74" s="0" t="n">
+      <c r="G74" s="1" t="n">
         <f aca="false">IF($D74=0,0,$E74/$D74)</f>
         <v>0.2</v>
       </c>
-      <c r="H74" s="0" t="n">
+      <c r="H74" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74)</f>
         <v>6</v>
       </c>
-      <c r="I74" s="0" t="str">
+      <c r="I74" s="1" t="str">
         <f aca="false">IF(AND($D74&gt;0,$H74=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="13" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B75" s="0" t="str">
+      <c r="B75" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
         <v>2</v>
       </c>
-      <c r="F75" s="0" t="n">
+      <c r="F75" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
         <v>5</v>
       </c>
-      <c r="G75" s="0" t="n">
+      <c r="G75" s="1" t="n">
         <f aca="false">IF($D75=0,0,$E75/$D75)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H75" s="0" t="n">
+      <c r="H75" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75)</f>
         <v>17</v>
       </c>
-      <c r="I75" s="0" t="str">
+      <c r="I75" s="1" t="str">
         <f aca="false">IF(AND($D75&gt;0,$H75=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="13" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B76" s="0" t="str">
+      <c r="B76" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="D76" s="0" t="n">
+      <c r="C76" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D76" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
         <v>6</v>
       </c>
-      <c r="F76" s="0" t="n">
+      <c r="F76" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
         <v>7</v>
       </c>
-      <c r="G76" s="0" t="n">
+      <c r="G76" s="1" t="n">
         <f aca="false">IF($D76=0,0,$E76/$D76)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76)</f>
         <v>26</v>
       </c>
-      <c r="I76" s="0" t="str">
+      <c r="I76" s="1" t="str">
         <f aca="false">IF(AND($D76&gt;0,$H76=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="13" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B77" s="0" t="str">
+      <c r="B77" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C77" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D77" s="0" t="n">
+      <c r="C77" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D77" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>22</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
         <v>11</v>
       </c>
-      <c r="F77" s="0" t="n">
+      <c r="F77" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
         <v>11</v>
       </c>
-      <c r="G77" s="0" t="n">
+      <c r="G77" s="1" t="n">
         <f aca="false">IF($D77=0,0,$E77/$D77)</f>
         <v>0.5</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77)</f>
         <v>40</v>
       </c>
-      <c r="I77" s="0" t="str">
+      <c r="I77" s="1" t="str">
         <f aca="false">IF(AND($D77&gt;0,$H77=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13" t="s">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B78" s="0" t="str">
+      <c r="B78" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
         <v>0</v>
       </c>
-      <c r="F78" s="0" t="n">
+      <c r="F78" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
         <v>0</v>
       </c>
-      <c r="G78" s="0" t="n">
+      <c r="G78" s="1" t="n">
         <f aca="false">IF($D78=0,0,$E78/$D78)</f>
         <v>0</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78)</f>
         <v>11</v>
       </c>
-      <c r="I78" s="0" t="str">
+      <c r="I78" s="1" t="str">
         <f aca="false">IF(AND($D78&gt;0,$H78=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
         <v>1842</v>
       </c>
-      <c r="B79" s="0" t="str">
+      <c r="B79" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="C79" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D79" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
         <v>0</v>
       </c>
-      <c r="F79" s="0" t="n">
+      <c r="F79" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
         <v>0</v>
       </c>
-      <c r="G79" s="0" t="n">
+      <c r="G79" s="1" t="n">
         <f aca="false">IF($D79=0,0,$E79/$D79)</f>
         <v>0</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79)</f>
         <v>20</v>
       </c>
-      <c r="I79" s="0" t="str">
+      <c r="I79" s="1" t="str">
         <f aca="false">IF(AND($D79&gt;0,$H79=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>

--- a/party-comparison-updated-v83.xlsx
+++ b/party-comparison-updated-v83.xlsx
@@ -133,7 +133,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">5 מדגמי הטלוויזיה (27.10.2026) מתוך סקרים לפי ערוץ - ללא ערוץ 16, שפרסם רק מדגם ראשון. מפלגה שאינה במדגמים = 0.</t>
+          <t xml:space="preserve">3 מדגמי הטלוויזיה (27.10.2026) מתוך סקרים לפי ערוץ: כאן חדשות, חדשות 12, חדשות 13. מפלגה שאינה במדגמים = 0.</t>
         </r>
       </text>
     </comment>
@@ -42090,16 +42090,16 @@
         <v>1474</v>
       </c>
       <c r="B2" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A2,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>27.8</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A2,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">ROUND(B2,0)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="n">
         <f aca="false">IF(C2&lt;=3,0,C2)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42107,8 +42107,8 @@
         <v>1488</v>
       </c>
       <c r="B3" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A3,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>20.8</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A3,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>21.3333333333333</v>
       </c>
       <c r="C3" s="1" t="n">
         <f aca="false">ROUND(B3,0)</f>
@@ -42124,8 +42124,8 @@
         <v>1489</v>
       </c>
       <c r="B4" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A4,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>12.8</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A4,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>12.6666666666667</v>
       </c>
       <c r="C4" s="1" t="n">
         <f aca="false">ROUND(B4,0)</f>
@@ -42141,7 +42141,7 @@
         <v>1477</v>
       </c>
       <c r="B5" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A5,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A5,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>9</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -42158,16 +42158,16 @@
         <v>1490</v>
       </c>
       <c r="B6" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A6,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>5.4</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A6,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>7.33333333333333</v>
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">ROUND(B6,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="n">
         <f aca="false">IF(C6&lt;=3,0,C6)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42175,16 +42175,16 @@
         <v>1479</v>
       </c>
       <c r="B7" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A7,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>7.4</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A7,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>6.33333333333333</v>
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">ROUND(B7,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1" t="n">
         <f aca="false">IF(C7&lt;=3,0,C7)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42192,8 +42192,8 @@
         <v>1481</v>
       </c>
       <c r="B8" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A8,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>6.4</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A8,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
         <f aca="false">ROUND(B8,0)</f>
@@ -42209,8 +42209,8 @@
         <v>1480</v>
       </c>
       <c r="B9" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A9,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>6.4</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A9,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="n">
         <f aca="false">ROUND(B9,0)</f>
@@ -42226,8 +42226,8 @@
         <v>1491</v>
       </c>
       <c r="B10" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A10,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>10.8</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A10,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>11.3333333333333</v>
       </c>
       <c r="C10" s="1" t="n">
         <f aca="false">ROUND(B10,0)</f>
@@ -42243,8 +42243,8 @@
         <v>1484</v>
       </c>
       <c r="B11" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A11,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
-        <v>6.2</v>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A11,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
         <f aca="false">ROUND(B11,0)</f>
@@ -42260,7 +42260,7 @@
         <v>1482</v>
       </c>
       <c r="B12" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A12,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A12,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>7</v>
       </c>
       <c r="C12" s="1" t="n">
@@ -42277,7 +42277,7 @@
         <v>1492</v>
       </c>
       <c r="B13" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A13,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A13,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -42294,7 +42294,7 @@
         <v>1493</v>
       </c>
       <c r="B14" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A14,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A14,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C14" s="1" t="n">
@@ -42311,7 +42311,7 @@
         <v>1494</v>
       </c>
       <c r="B15" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A15,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A15,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C15" s="1" t="n">
@@ -42328,7 +42328,7 @@
         <v>1495</v>
       </c>
       <c r="B16" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A16,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A16,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -42345,7 +42345,7 @@
         <v>1496</v>
       </c>
       <c r="B17" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A17,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A17,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C17" s="1" t="n">
@@ -42362,7 +42362,7 @@
         <v>1497</v>
       </c>
       <c r="B18" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A18,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A18,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -42379,7 +42379,7 @@
         <v>1498</v>
       </c>
       <c r="B19" s="1" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A19,'סקרים לפי ערוץ'!$E$1:$R$1,0)),'סקרים לפי ערוץ'!$A:$A,"&lt;&gt;ערוץ 16"),0)</f>
+        <f aca="false">IFERROR(SUMPRODUCT(SUMIF('סקרים לפי ערוץ'!$A:$A,{"כאן חדשות","חדשות 12","חדשות 13"},INDEX('סקרים לפי ערוץ'!$E:$R,0,MATCH($A19,'סקרים לפי ערוץ'!$E$1:$R$1,0))))/3,0)</f>
         <v>0</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -46734,7 +46734,7 @@
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A2,'סקר 2026'!$A:$A,0))</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A2,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B2)</f>
@@ -46742,11 +46742,11 @@
       </c>
       <c r="D2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A2,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B2)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="n">
         <f aca="false">IF(B2=0,0,C2/B2)</f>
-        <v>0.142857142857143</v>
+        <v>0.148148148148148</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>1812</v>
@@ -46870,7 +46870,7 @@
       </c>
       <c r="B6" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A6,'סקר 2026'!$A:$A,0))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B6)</f>
@@ -46878,11 +46878,11 @@
       </c>
       <c r="D6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B6)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">IF(B6=0,0,C6/B6)</f>
-        <v>0.4</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>1816</v>
@@ -46904,7 +46904,7 @@
       </c>
       <c r="B7" s="1" t="n">
         <f aca="false">INDEX('סקר 2026'!$D:$D,MATCH(A7,'סקר 2026'!$A:$A,0))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A7,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;B7)</f>
@@ -46912,7 +46912,7 @@
       </c>
       <c r="D7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A7,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B7)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">IF(B7=0,0,C7/B7)</f>

--- a/party-comparison-updated-v83.xlsx
+++ b/party-comparison-updated-v83.xlsx
@@ -337,6 +337,74 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="A8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ממוצע מעוגל של </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5 מדגמי הטלוויזיה (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">חדשות </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">12, חדשות 13, כאן חדשות, ערוץ 14, i24 news). </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ערכים קבועים ולא נוסחה, כי </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">update_html_from_xlsx.py </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">קורא את הגיליון בלי ערכים מחושבים. אם מדגם משתנה - יש לעדכן גם שורה זו</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B2" authorId="0">
       <text>
         <r>
@@ -502,7 +570,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7583" uniqueCount="1858">
   <si>
     <t xml:space="preserve">מפלגה</t>
   </si>
@@ -7301,13 +7369,393 @@
     <t xml:space="preserve">יצחק כ״ץ</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ממוצע </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">מדגמים</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ממוצע</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 12, 13, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">כאן</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 14, i24</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">מנדטים</t>
   </si>
   <si>
-    <t xml:space="preserve">מועמדים ידועים (סה"כ)</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">מועמדים ידועים </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">סה</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">כ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">הערה</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">חדשות </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ש</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ס</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">רע</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">מ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ביחד </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">בנט</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">לפיד</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ישר</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">המילואימניקים</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">הכלכלית</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">חדשות </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ערוץ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ערוץ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -7482,7 +7930,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7532,6 +7980,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -47254,7 +47706,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47628,6 +48080,59 @@
         <v>0</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -47648,2843 +48153,3311 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
         <v>1827</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="13" t="s">
         <v>1828</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>1844</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="13" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1472</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="13" t="s">
         <v>1473</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="13" t="s">
         <v>1807</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>1845</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B2" s="1" t="str">
+      <c r="H1" s="13" t="s">
+        <v>1847</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B2" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="13" t="s">
         <v>1474</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
         <v>23</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="0" t="n">
         <f aca="false">IF($D2=0,0,$E2/$D2)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2)</f>
         <v>36</v>
       </c>
-      <c r="I2" s="1" t="str">
+      <c r="I2" s="0" t="str">
         <f aca="false">IF(AND($D2&gt;0,$H2=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B3" s="1" t="str">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B3" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="13" t="s">
         <v>1480</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="0" t="n">
         <f aca="false">IF($D3=0,0,$E3/$D3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3)</f>
         <v>9</v>
       </c>
-      <c r="I3" s="1" t="str">
+      <c r="I3" s="0" t="str">
         <f aca="false">IF(AND($D3&gt;0,$H3=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B4" s="1" t="str">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B4" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="C4" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="0" t="n">
         <f aca="false">IF($D4=0,0,$E4/$D4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4)</f>
         <v>11</v>
       </c>
-      <c r="I4" s="1" t="str">
+      <c r="I4" s="0" t="str">
         <f aca="false">IF(AND($D4&gt;0,$H4=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B5" s="1" t="str">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B5" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="13" t="s">
         <v>1491</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>12</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="0" t="n">
         <f aca="false">IF($D5=0,0,$E5/$D5)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5)</f>
         <v>10</v>
       </c>
-      <c r="I5" s="1" t="str">
+      <c r="I5" s="0" t="str">
         <f aca="false">IF(AND($D5&gt;0,$H5=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B6" s="1" t="str">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B6" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="13" t="s">
         <v>1490</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
         <v>2</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
         <v>5</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="0" t="n">
         <f aca="false">IF($D6=0,0,$E6/$D6)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6)</f>
         <v>20</v>
       </c>
-      <c r="I6" s="1" t="str">
+      <c r="I6" s="0" t="str">
         <f aca="false">IF(AND($D6&gt;0,$H6=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B7" s="1" t="str">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B7" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="0" t="n">
         <f aca="false">IF($D7=0,0,$E7/$D7)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7)</f>
         <v>20</v>
       </c>
-      <c r="I7" s="1" t="str">
+      <c r="I7" s="0" t="str">
         <f aca="false">IF(AND($D7&gt;0,$H7=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B8" s="1" t="str">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B8" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="0" t="n">
         <f aca="false">IF($D8=0,0,$E8/$D8)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8)</f>
         <v>18</v>
       </c>
-      <c r="I8" s="1" t="str">
+      <c r="I8" s="0" t="str">
         <f aca="false">IF(AND($D8&gt;0,$H8=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B9" s="1" t="str">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B9" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="C9" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
         <v>5</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="0" t="n">
         <f aca="false">IF($D9=0,0,$E9/$D9)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9)</f>
         <v>6</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="I9" s="0" t="str">
         <f aca="false">IF(AND($D9&gt;0,$H9=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B10" s="1" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B10" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="13" t="s">
         <v>1481</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
         <v>4</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="0" t="n">
         <f aca="false">IF($D10=0,0,$E10/$D10)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10)</f>
         <v>17</v>
       </c>
-      <c r="I10" s="1" t="str">
+      <c r="I10" s="0" t="str">
         <f aca="false">IF(AND($D10&gt;0,$H10=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B11" s="1" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B11" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="C11" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D11" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>12</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="0" t="n">
         <f aca="false">IF($D11=0,0,$E11/$D11)</f>
         <v>0.5</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11)</f>
         <v>26</v>
       </c>
-      <c r="I11" s="1" t="str">
+      <c r="I11" s="0" t="str">
         <f aca="false">IF(AND($D11&gt;0,$H11=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B12" s="1" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B12" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="C12" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
         <v>11</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
         <v>10</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="0" t="n">
         <f aca="false">IF($D12=0,0,$E12/$D12)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12)</f>
         <v>40</v>
       </c>
-      <c r="I12" s="1" t="str">
+      <c r="I12" s="0" t="str">
         <f aca="false">IF(AND($D12&gt;0,$H12=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B13" s="1" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B13" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="13" t="s">
         <v>1495</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="0" t="n">
         <f aca="false">IF($D13=0,0,$E13/$D13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13)</f>
         <v>11</v>
       </c>
-      <c r="I13" s="1" t="str">
+      <c r="I13" s="0" t="str">
         <f aca="false">IF(AND($D13&gt;0,$H13=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B14" s="1" t="str">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B14" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="C14" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="0" t="n">
         <f aca="false">IF($D14=0,0,$E14/$D14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14)</f>
         <v>20</v>
       </c>
-      <c r="I14" s="1" t="str">
+      <c r="I14" s="0" t="str">
         <f aca="false">IF(AND($D14&gt;0,$H14=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B15" s="1" t="str">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B15" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="13" t="s">
         <v>1474</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
         <v>4</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
         <v>23</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="0" t="n">
         <f aca="false">IF($D15=0,0,$E15/$D15)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15)</f>
         <v>36</v>
       </c>
-      <c r="I15" s="1" t="str">
+      <c r="I15" s="0" t="str">
         <f aca="false">IF(AND($D15&gt;0,$H15=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B16" s="1" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B16" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="13" t="s">
         <v>1480</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
         <v>6</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="0" t="n">
         <f aca="false">IF($D16=0,0,$E16/$D16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16)</f>
         <v>9</v>
       </c>
-      <c r="I16" s="1" t="str">
+      <c r="I16" s="0" t="str">
         <f aca="false">IF(AND($D16&gt;0,$H16=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B17" s="1" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B17" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="C17" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
         <v>6</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="0" t="n">
         <f aca="false">IF($D17=0,0,$E17/$D17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17)</f>
         <v>11</v>
       </c>
-      <c r="I17" s="1" t="str">
+      <c r="I17" s="0" t="str">
         <f aca="false">IF(AND($D17&gt;0,$H17=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B18" s="1" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B18" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="13" t="s">
         <v>1491</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
         <v>2</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
         <v>8</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="0" t="n">
         <f aca="false">IF($D18=0,0,$E18/$D18)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18)</f>
         <v>10</v>
       </c>
-      <c r="I18" s="1" t="str">
+      <c r="I18" s="0" t="str">
         <f aca="false">IF(AND($D18&gt;0,$H18=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B19" s="1" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B19" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="13" t="s">
         <v>1490</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
         <v>2</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
         <v>5</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="0" t="n">
         <f aca="false">IF($D19=0,0,$E19/$D19)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19)</f>
         <v>20</v>
       </c>
-      <c r="I19" s="1" t="str">
+      <c r="I19" s="0" t="str">
         <f aca="false">IF(AND($D19&gt;0,$H19=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B20" s="1" t="str">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B20" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
         <v>4</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
         <v>5</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="0" t="n">
         <f aca="false">IF($D20=0,0,$E20/$D20)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20)</f>
         <v>20</v>
       </c>
-      <c r="I20" s="1" t="str">
+      <c r="I20" s="0" t="str">
         <f aca="false">IF(AND($D20&gt;0,$H20=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B21" s="1" t="str">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B21" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D21" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="G21" s="0" t="n">
         <f aca="false">IF($D21=0,0,$E21/$D21)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21)</f>
         <v>18</v>
       </c>
-      <c r="I21" s="1" t="str">
+      <c r="I21" s="0" t="str">
         <f aca="false">IF(AND($D21&gt;0,$H21=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B22" s="1" t="str">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B22" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="C22" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D22" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
         <v>1</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
         <v>5</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="0" t="n">
         <f aca="false">IF($D22=0,0,$E22/$D22)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22)</f>
         <v>6</v>
       </c>
-      <c r="I22" s="1" t="str">
+      <c r="I22" s="0" t="str">
         <f aca="false">IF(AND($D22&gt;0,$H22=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B23" s="1" t="str">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B23" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="13" t="s">
         <v>1481</v>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D23" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
         <v>4</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="G23" s="0" t="n">
         <f aca="false">IF($D23=0,0,$E23/$D23)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23)</f>
         <v>17</v>
       </c>
-      <c r="I23" s="1" t="str">
+      <c r="I23" s="0" t="str">
         <f aca="false">IF(AND($D23&gt;0,$H23=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B24" s="1" t="str">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B24" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="C24" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D24" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
         <v>6</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
         <v>7</v>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="G24" s="0" t="n">
         <f aca="false">IF($D24=0,0,$E24/$D24)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24)</f>
         <v>26</v>
       </c>
-      <c r="I24" s="1" t="str">
+      <c r="I24" s="0" t="str">
         <f aca="false">IF(AND($D24&gt;0,$H24=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B25" s="1" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B25" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="C25" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D25" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>22</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
         <v>11</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
         <v>11</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="G25" s="0" t="n">
         <f aca="false">IF($D25=0,0,$E25/$D25)</f>
         <v>0.5</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25)</f>
         <v>40</v>
       </c>
-      <c r="I25" s="1" t="str">
+      <c r="I25" s="0" t="str">
         <f aca="false">IF(AND($D25&gt;0,$H25=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B26" s="1" t="str">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B26" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="13" t="s">
         <v>1495</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D26" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="G26" s="0" t="n">
         <f aca="false">IF($D26=0,0,$E26/$D26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26)</f>
         <v>11</v>
       </c>
-      <c r="I26" s="1" t="str">
+      <c r="I26" s="0" t="str">
         <f aca="false">IF(AND($D26&gt;0,$H26=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B27" s="1" t="str">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B27" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="C27" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D27" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="G27" s="0" t="n">
         <f aca="false">IF($D27=0,0,$E27/$D27)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27)</f>
         <v>20</v>
       </c>
-      <c r="I27" s="1" t="str">
+      <c r="I27" s="0" t="str">
         <f aca="false">IF(AND($D27&gt;0,$H27=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B28" s="1" t="str">
+      <c r="B28" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="13" t="s">
         <v>1474</v>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D28" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
         <v>23</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="G28" s="0" t="n">
         <f aca="false">IF($D28=0,0,$E28/$D28)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28)</f>
         <v>36</v>
       </c>
-      <c r="I28" s="1" t="str">
+      <c r="I28" s="0" t="str">
         <f aca="false">IF(AND($D28&gt;0,$H28=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B29" s="1" t="str">
+      <c r="B29" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="13" t="s">
         <v>1480</v>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D29" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="F29" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
         <v>6</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="G29" s="0" t="n">
         <f aca="false">IF($D29=0,0,$E29/$D29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29)</f>
         <v>9</v>
       </c>
-      <c r="I29" s="1" t="str">
+      <c r="I29" s="0" t="str">
         <f aca="false">IF(AND($D29&gt;0,$H29=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B30" s="1" t="str">
+      <c r="B30" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D30" s="1" t="n">
+      <c r="C30" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D30" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
         <v>6</v>
       </c>
-      <c r="G30" s="1" t="n">
+      <c r="G30" s="0" t="n">
         <f aca="false">IF($D30=0,0,$E30/$D30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30)</f>
         <v>11</v>
       </c>
-      <c r="I30" s="1" t="str">
+      <c r="I30" s="0" t="str">
         <f aca="false">IF(AND($D30&gt;0,$H30=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B31" s="1" t="str">
+      <c r="B31" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="13" t="s">
         <v>1491</v>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D31" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
         <v>2</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
         <v>8</v>
       </c>
-      <c r="G31" s="1" t="n">
+      <c r="G31" s="0" t="n">
         <f aca="false">IF($D31=0,0,$E31/$D31)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31)</f>
         <v>10</v>
       </c>
-      <c r="I31" s="1" t="str">
+      <c r="I31" s="0" t="str">
         <f aca="false">IF(AND($D31&gt;0,$H31=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B32" s="1" t="str">
+      <c r="B32" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="13" t="s">
         <v>1490</v>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D32" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>8</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
         <v>2</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
         <v>6</v>
       </c>
-      <c r="G32" s="1" t="n">
+      <c r="G32" s="0" t="n">
         <f aca="false">IF($D32=0,0,$E32/$D32)</f>
         <v>0.25</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32)</f>
         <v>20</v>
       </c>
-      <c r="I32" s="1" t="str">
+      <c r="I32" s="0" t="str">
         <f aca="false">IF(AND($D32&gt;0,$H32=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B33" s="1" t="str">
+      <c r="B33" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D33" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
         <v>4</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
         <v>5</v>
       </c>
-      <c r="G33" s="1" t="n">
+      <c r="G33" s="0" t="n">
         <f aca="false">IF($D33=0,0,$E33/$D33)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="H33" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33)</f>
         <v>20</v>
       </c>
-      <c r="I33" s="1" t="str">
+      <c r="I33" s="0" t="str">
         <f aca="false">IF(AND($D33&gt;0,$H33=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B34" s="1" t="str">
+      <c r="B34" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D34" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="F34" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
         <v>5</v>
       </c>
-      <c r="G34" s="1" t="n">
+      <c r="G34" s="0" t="n">
         <f aca="false">IF($D34=0,0,$E34/$D34)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34)</f>
         <v>18</v>
       </c>
-      <c r="I34" s="1" t="str">
+      <c r="I34" s="0" t="str">
         <f aca="false">IF(AND($D34&gt;0,$H34=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B35" s="1" t="str">
+      <c r="B35" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D35" s="1" t="n">
+      <c r="C35" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D35" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
         <v>1</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
         <v>5</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="G35" s="0" t="n">
         <f aca="false">IF($D35=0,0,$E35/$D35)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H35" s="1" t="n">
+      <c r="H35" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35)</f>
         <v>6</v>
       </c>
-      <c r="I35" s="1" t="str">
+      <c r="I35" s="0" t="str">
         <f aca="false">IF(AND($D35&gt;0,$H35=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B36" s="1" t="str">
+      <c r="B36" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="13" t="s">
         <v>1481</v>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D36" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
         <v>2</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
         <v>4</v>
       </c>
-      <c r="G36" s="1" t="n">
+      <c r="G36" s="0" t="n">
         <f aca="false">IF($D36=0,0,$E36/$D36)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="H36" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36)</f>
         <v>17</v>
       </c>
-      <c r="I36" s="1" t="str">
+      <c r="I36" s="0" t="str">
         <f aca="false">IF(AND($D36&gt;0,$H36=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B37" s="1" t="str">
+      <c r="B37" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D37" s="1" t="n">
+      <c r="C37" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D37" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
         <v>6</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
         <v>7</v>
       </c>
-      <c r="G37" s="1" t="n">
+      <c r="G37" s="0" t="n">
         <f aca="false">IF($D37=0,0,$E37/$D37)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37)</f>
         <v>26</v>
       </c>
-      <c r="I37" s="1" t="str">
+      <c r="I37" s="0" t="str">
         <f aca="false">IF(AND($D37&gt;0,$H37=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B38" s="1" t="str">
+      <c r="B38" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D38" s="1" t="n">
+      <c r="C38" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D38" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
         <v>11</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
         <v>10</v>
       </c>
-      <c r="G38" s="1" t="n">
+      <c r="G38" s="0" t="n">
         <f aca="false">IF($D38=0,0,$E38/$D38)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="H38" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38)</f>
         <v>40</v>
       </c>
-      <c r="I38" s="1" t="str">
+      <c r="I38" s="0" t="str">
         <f aca="false">IF(AND($D38&gt;0,$H38=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B39" s="1" t="str">
+      <c r="B39" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="13" t="s">
         <v>1495</v>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D39" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="1" t="n">
+      <c r="G39" s="0" t="n">
         <f aca="false">IF($D39=0,0,$E39/$D39)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39)</f>
         <v>11</v>
       </c>
-      <c r="I39" s="1" t="str">
+      <c r="I39" s="0" t="str">
         <f aca="false">IF(AND($D39&gt;0,$H39=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
         <v>1836</v>
       </c>
-      <c r="B40" s="1" t="str">
+      <c r="B40" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D40" s="1" t="n">
+      <c r="C40" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D40" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="1" t="n">
+      <c r="G40" s="0" t="n">
         <f aca="false">IF($D40=0,0,$E40/$D40)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40)</f>
         <v>20</v>
       </c>
-      <c r="I40" s="1" t="str">
+      <c r="I40" s="0" t="str">
         <f aca="false">IF(AND($D40&gt;0,$H40=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B41" s="1" t="str">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B41" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="13" t="s">
         <v>1474</v>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D41" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>31</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
         <v>4</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="F41" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
         <v>27</v>
       </c>
-      <c r="G41" s="1" t="n">
+      <c r="G41" s="0" t="n">
         <f aca="false">IF($D41=0,0,$E41/$D41)</f>
         <v>0.129032258064516</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41)</f>
         <v>36</v>
       </c>
-      <c r="I41" s="1" t="str">
+      <c r="I41" s="0" t="str">
         <f aca="false">IF(AND($D41&gt;0,$H41=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B42" s="1" t="str">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B42" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="13" t="s">
         <v>1480</v>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D42" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="F42" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
         <v>7</v>
       </c>
-      <c r="G42" s="1" t="n">
+      <c r="G42" s="0" t="n">
         <f aca="false">IF($D42=0,0,$E42/$D42)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="H42" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42)</f>
         <v>9</v>
       </c>
-      <c r="I42" s="1" t="str">
+      <c r="I42" s="0" t="str">
         <f aca="false">IF(AND($D42&gt;0,$H42=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B43" s="1" t="str">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B43" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D43" s="1" t="n">
+      <c r="C43" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D43" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>10</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="F43" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
         <v>10</v>
       </c>
-      <c r="G43" s="1" t="n">
+      <c r="G43" s="0" t="n">
         <f aca="false">IF($D43=0,0,$E43/$D43)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="1" t="n">
+      <c r="H43" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43)</f>
         <v>11</v>
       </c>
-      <c r="I43" s="1" t="str">
+      <c r="I43" s="0" t="str">
         <f aca="false">IF(AND($D43&gt;0,$H43=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B44" s="1" t="str">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B44" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="13" t="s">
         <v>1491</v>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D44" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
         <v>2</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="F44" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
         <v>8</v>
       </c>
-      <c r="G44" s="1" t="n">
+      <c r="G44" s="0" t="n">
         <f aca="false">IF($D44=0,0,$E44/$D44)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="H44" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44)</f>
         <v>10</v>
       </c>
-      <c r="I44" s="1" t="str">
+      <c r="I44" s="0" t="str">
         <f aca="false">IF(AND($D44&gt;0,$H44=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B45" s="1" t="str">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B45" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="13" t="s">
         <v>1490</v>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D45" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="F45" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="1" t="n">
+      <c r="G45" s="0" t="n">
         <f aca="false">IF($D45=0,0,$E45/$D45)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="1" t="n">
+      <c r="H45" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45)</f>
         <v>20</v>
       </c>
-      <c r="I45" s="1" t="str">
+      <c r="I45" s="0" t="str">
         <f aca="false">IF(AND($D45&gt;0,$H45=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B46" s="1" t="str">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B46" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D46" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
         <v>4</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
         <v>5</v>
       </c>
-      <c r="G46" s="1" t="n">
+      <c r="G46" s="0" t="n">
         <f aca="false">IF($D46=0,0,$E46/$D46)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H46" s="1" t="n">
+      <c r="H46" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46)</f>
         <v>20</v>
       </c>
-      <c r="I46" s="1" t="str">
+      <c r="I46" s="0" t="str">
         <f aca="false">IF(AND($D46&gt;0,$H46=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B47" s="1" t="str">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B47" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D47" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
         <v>1</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="F47" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
         <v>6</v>
       </c>
-      <c r="G47" s="1" t="n">
+      <c r="G47" s="0" t="n">
         <f aca="false">IF($D47=0,0,$E47/$D47)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H47" s="1" t="n">
+      <c r="H47" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47)</f>
         <v>18</v>
       </c>
-      <c r="I47" s="1" t="str">
+      <c r="I47" s="0" t="str">
         <f aca="false">IF(AND($D47&gt;0,$H47=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B48" s="1" t="str">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B48" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D48" s="1" t="n">
+      <c r="C48" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D48" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
         <v>1</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="F48" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
         <v>5</v>
       </c>
-      <c r="G48" s="1" t="n">
+      <c r="G48" s="0" t="n">
         <f aca="false">IF($D48=0,0,$E48/$D48)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H48" s="1" t="n">
+      <c r="H48" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48)</f>
         <v>6</v>
       </c>
-      <c r="I48" s="1" t="str">
+      <c r="I48" s="0" t="str">
         <f aca="false">IF(AND($D48&gt;0,$H48=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B49" s="1" t="str">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B49" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="13" t="s">
         <v>1481</v>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D49" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
         <v>2</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="F49" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
         <v>5</v>
       </c>
-      <c r="G49" s="1" t="n">
+      <c r="G49" s="0" t="n">
         <f aca="false">IF($D49=0,0,$E49/$D49)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="H49" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49)</f>
         <v>17</v>
       </c>
-      <c r="I49" s="1" t="str">
+      <c r="I49" s="0" t="str">
         <f aca="false">IF(AND($D49&gt;0,$H49=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B50" s="1" t="str">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B50" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D50" s="1" t="n">
+      <c r="C50" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D50" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
         <v>6</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="F50" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
         <v>5</v>
       </c>
-      <c r="G50" s="1" t="n">
+      <c r="G50" s="0" t="n">
         <f aca="false">IF($D50=0,0,$E50/$D50)</f>
         <v>0.545454545454545</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="H50" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50)</f>
         <v>26</v>
       </c>
-      <c r="I50" s="1" t="str">
+      <c r="I50" s="0" t="str">
         <f aca="false">IF(AND($D50&gt;0,$H50=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B51" s="1" t="str">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B51" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D51" s="1" t="n">
+      <c r="C51" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D51" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>20</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
         <v>10</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="F51" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
         <v>10</v>
       </c>
-      <c r="G51" s="1" t="n">
+      <c r="G51" s="0" t="n">
         <f aca="false">IF($D51=0,0,$E51/$D51)</f>
         <v>0.5</v>
       </c>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51)</f>
         <v>40</v>
       </c>
-      <c r="I51" s="1" t="str">
+      <c r="I51" s="0" t="str">
         <f aca="false">IF(AND($D51&gt;0,$H51=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B52" s="1" t="str">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B52" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="13" t="s">
         <v>1495</v>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D52" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
         <v>0</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="F52" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="1" t="n">
+      <c r="G52" s="0" t="n">
         <f aca="false">IF($D52=0,0,$E52/$D52)</f>
         <v>0</v>
       </c>
-      <c r="H52" s="1" t="n">
+      <c r="H52" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52)</f>
         <v>11</v>
       </c>
-      <c r="I52" s="1" t="str">
+      <c r="I52" s="0" t="str">
         <f aca="false">IF(AND($D52&gt;0,$H52=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B53" s="1" t="str">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="13" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B53" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D53" s="1" t="n">
+      <c r="C53" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D53" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
         <v>0</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
         <v>0</v>
       </c>
-      <c r="G53" s="1" t="n">
+      <c r="G53" s="0" t="n">
         <f aca="false">IF($D53=0,0,$E53/$D53)</f>
         <v>0</v>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="H53" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53)</f>
         <v>20</v>
       </c>
-      <c r="I53" s="1" t="str">
+      <c r="I53" s="0" t="str">
         <f aca="false">IF(AND($D53&gt;0,$H53=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B54" s="1" t="str">
+      <c r="B54" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="13" t="s">
         <v>1474</v>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="D54" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
         <v>4</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="F54" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
         <v>23</v>
       </c>
-      <c r="G54" s="1" t="n">
+      <c r="G54" s="0" t="n">
         <f aca="false">IF($D54=0,0,$E54/$D54)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="H54" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54)</f>
         <v>36</v>
       </c>
-      <c r="I54" s="1" t="str">
+      <c r="I54" s="0" t="str">
         <f aca="false">IF(AND($D54&gt;0,$H54=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B55" s="1" t="str">
+      <c r="B55" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="13" t="s">
         <v>1480</v>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="D55" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
         <v>7</v>
       </c>
-      <c r="G55" s="1" t="n">
+      <c r="G55" s="0" t="n">
         <f aca="false">IF($D55=0,0,$E55/$D55)</f>
         <v>0</v>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="H55" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55)</f>
         <v>9</v>
       </c>
-      <c r="I55" s="1" t="str">
+      <c r="I55" s="0" t="str">
         <f aca="false">IF(AND($D55&gt;0,$H55=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B56" s="1" t="str">
+      <c r="B56" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D56" s="1" t="n">
+      <c r="C56" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D56" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>8</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
         <v>0</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="F56" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
         <v>8</v>
       </c>
-      <c r="G56" s="1" t="n">
+      <c r="G56" s="0" t="n">
         <f aca="false">IF($D56=0,0,$E56/$D56)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56)</f>
         <v>11</v>
       </c>
-      <c r="I56" s="1" t="str">
+      <c r="I56" s="0" t="str">
         <f aca="false">IF(AND($D56&gt;0,$H56=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B57" s="1" t="str">
+      <c r="B57" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="13" t="s">
         <v>1491</v>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D57" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
         <v>2</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="F57" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
         <v>7</v>
       </c>
-      <c r="G57" s="1" t="n">
+      <c r="G57" s="0" t="n">
         <f aca="false">IF($D57=0,0,$E57/$D57)</f>
         <v>0.222222222222222</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57)</f>
         <v>10</v>
       </c>
-      <c r="I57" s="1" t="str">
+      <c r="I57" s="0" t="str">
         <f aca="false">IF(AND($D57&gt;0,$H57=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B58" s="1" t="str">
+      <c r="B58" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="13" t="s">
         <v>1490</v>
       </c>
-      <c r="D58" s="1" t="n">
+      <c r="D58" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
         <v>2</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="F58" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
         <v>3</v>
       </c>
-      <c r="G58" s="1" t="n">
+      <c r="G58" s="0" t="n">
         <f aca="false">IF($D58=0,0,$E58/$D58)</f>
         <v>0.4</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58)</f>
         <v>20</v>
       </c>
-      <c r="I58" s="1" t="str">
+      <c r="I58" s="0" t="str">
         <f aca="false">IF(AND($D58&gt;0,$H58=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B59" s="1" t="str">
+      <c r="B59" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="D59" s="1" t="n">
+      <c r="D59" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
         <v>4</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="F59" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
         <v>5</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="G59" s="0" t="n">
         <f aca="false">IF($D59=0,0,$E59/$D59)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59)</f>
         <v>20</v>
       </c>
-      <c r="I59" s="1" t="str">
+      <c r="I59" s="0" t="str">
         <f aca="false">IF(AND($D59&gt;0,$H59=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B60" s="1" t="str">
+      <c r="B60" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="D60" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
         <v>1</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="F60" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
         <v>5</v>
       </c>
-      <c r="G60" s="1" t="n">
+      <c r="G60" s="0" t="n">
         <f aca="false">IF($D60=0,0,$E60/$D60)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="H60" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60)</f>
         <v>18</v>
       </c>
-      <c r="I60" s="1" t="str">
+      <c r="I60" s="0" t="str">
         <f aca="false">IF(AND($D60&gt;0,$H60=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B61" s="1" t="str">
+      <c r="B61" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D61" s="1" t="n">
+      <c r="C61" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D61" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
         <v>1</v>
       </c>
-      <c r="F61" s="1" t="n">
+      <c r="F61" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
         <v>5</v>
       </c>
-      <c r="G61" s="1" t="n">
+      <c r="G61" s="0" t="n">
         <f aca="false">IF($D61=0,0,$E61/$D61)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H61" s="1" t="n">
+      <c r="H61" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61)</f>
         <v>6</v>
       </c>
-      <c r="I61" s="1" t="str">
+      <c r="I61" s="0" t="str">
         <f aca="false">IF(AND($D61&gt;0,$H61=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B62" s="1" t="str">
+      <c r="B62" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="13" t="s">
         <v>1481</v>
       </c>
-      <c r="D62" s="1" t="n">
+      <c r="D62" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
         <v>2</v>
       </c>
-      <c r="F62" s="1" t="n">
+      <c r="F62" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
         <v>5</v>
       </c>
-      <c r="G62" s="1" t="n">
+      <c r="G62" s="0" t="n">
         <f aca="false">IF($D62=0,0,$E62/$D62)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="H62" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62)</f>
         <v>17</v>
       </c>
-      <c r="I62" s="1" t="str">
+      <c r="I62" s="0" t="str">
         <f aca="false">IF(AND($D62&gt;0,$H62=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B63" s="1" t="str">
+      <c r="B63" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D63" s="1" t="n">
+      <c r="C63" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D63" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>15</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
         <v>6</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F63" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
         <v>9</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G63" s="0" t="n">
         <f aca="false">IF($D63=0,0,$E63/$D63)</f>
         <v>0.4</v>
       </c>
-      <c r="H63" s="1" t="n">
+      <c r="H63" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63)</f>
         <v>26</v>
       </c>
-      <c r="I63" s="1" t="str">
+      <c r="I63" s="0" t="str">
         <f aca="false">IF(AND($D63&gt;0,$H63=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B64" s="1" t="str">
+      <c r="B64" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D64" s="1" t="n">
+      <c r="C64" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D64" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>20</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
         <v>10</v>
       </c>
-      <c r="F64" s="1" t="n">
+      <c r="F64" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
         <v>10</v>
       </c>
-      <c r="G64" s="1" t="n">
+      <c r="G64" s="0" t="n">
         <f aca="false">IF($D64=0,0,$E64/$D64)</f>
         <v>0.5</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="H64" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64)</f>
         <v>40</v>
       </c>
-      <c r="I64" s="1" t="str">
+      <c r="I64" s="0" t="str">
         <f aca="false">IF(AND($D64&gt;0,$H64=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B65" s="1" t="str">
+      <c r="B65" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="13" t="s">
         <v>1495</v>
       </c>
-      <c r="D65" s="1" t="n">
+      <c r="D65" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
         <v>0</v>
       </c>
-      <c r="F65" s="1" t="n">
+      <c r="F65" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
         <v>0</v>
       </c>
-      <c r="G65" s="1" t="n">
+      <c r="G65" s="0" t="n">
         <f aca="false">IF($D65=0,0,$E65/$D65)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="1" t="n">
+      <c r="H65" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65)</f>
         <v>11</v>
       </c>
-      <c r="I65" s="1" t="str">
+      <c r="I65" s="0" t="str">
         <f aca="false">IF(AND($D65&gt;0,$H65=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
         <v>1840</v>
       </c>
-      <c r="B66" s="1" t="str">
+      <c r="B66" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D66" s="1" t="n">
+      <c r="C66" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D66" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
         <v>0</v>
       </c>
-      <c r="F66" s="1" t="n">
+      <c r="F66" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
         <v>0</v>
       </c>
-      <c r="G66" s="1" t="n">
+      <c r="G66" s="0" t="n">
         <f aca="false">IF($D66=0,0,$E66/$D66)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="1" t="n">
+      <c r="H66" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66)</f>
         <v>20</v>
       </c>
-      <c r="I66" s="1" t="str">
+      <c r="I66" s="0" t="str">
         <f aca="false">IF(AND($D66&gt;0,$H66=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B67" s="1" t="str">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B67" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="13" t="s">
         <v>1474</v>
       </c>
-      <c r="D67" s="1" t="n">
+      <c r="D67" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>25</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
         <v>4</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="F67" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
         <v>21</v>
       </c>
-      <c r="G67" s="1" t="n">
+      <c r="G67" s="0" t="n">
         <f aca="false">IF($D67=0,0,$E67/$D67)</f>
         <v>0.16</v>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="H67" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67)</f>
         <v>36</v>
       </c>
-      <c r="I67" s="1" t="str">
+      <c r="I67" s="0" t="str">
         <f aca="false">IF(AND($D67&gt;0,$H67=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B68" s="1" t="str">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B68" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="13" t="s">
         <v>1480</v>
       </c>
-      <c r="D68" s="1" t="n">
+      <c r="D68" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
         <v>0</v>
       </c>
-      <c r="F68" s="1" t="n">
+      <c r="F68" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
         <v>7</v>
       </c>
-      <c r="G68" s="1" t="n">
+      <c r="G68" s="0" t="n">
         <f aca="false">IF($D68=0,0,$E68/$D68)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="H68" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68)</f>
         <v>9</v>
       </c>
-      <c r="I68" s="1" t="str">
+      <c r="I68" s="0" t="str">
         <f aca="false">IF(AND($D68&gt;0,$H68=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B69" s="1" t="str">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B69" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D69" s="1" t="n">
+      <c r="C69" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D69" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
         <v>0</v>
       </c>
-      <c r="F69" s="1" t="n">
+      <c r="F69" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
         <v>7</v>
       </c>
-      <c r="G69" s="1" t="n">
+      <c r="G69" s="0" t="n">
         <f aca="false">IF($D69=0,0,$E69/$D69)</f>
         <v>0</v>
       </c>
-      <c r="H69" s="1" t="n">
+      <c r="H69" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69)</f>
         <v>11</v>
       </c>
-      <c r="I69" s="1" t="str">
+      <c r="I69" s="0" t="str">
         <f aca="false">IF(AND($D69&gt;0,$H69=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B70" s="1" t="str">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B70" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="13" t="s">
         <v>1491</v>
       </c>
-      <c r="D70" s="1" t="n">
+      <c r="D70" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
         <v>2</v>
       </c>
-      <c r="F70" s="1" t="n">
+      <c r="F70" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
         <v>8</v>
       </c>
-      <c r="G70" s="1" t="n">
+      <c r="G70" s="0" t="n">
         <f aca="false">IF($D70=0,0,$E70/$D70)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H70" s="1" t="n">
+      <c r="H70" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70)</f>
         <v>10</v>
       </c>
-      <c r="I70" s="1" t="str">
+      <c r="I70" s="0" t="str">
         <f aca="false">IF(AND($D70&gt;0,$H70=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B71" s="1" t="str">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B71" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="13" t="s">
         <v>1490</v>
       </c>
-      <c r="D71" s="1" t="n">
+      <c r="D71" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
         <v>2</v>
       </c>
-      <c r="F71" s="1" t="n">
+      <c r="F71" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
         <v>4</v>
       </c>
-      <c r="G71" s="1" t="n">
+      <c r="G71" s="0" t="n">
         <f aca="false">IF($D71=0,0,$E71/$D71)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="H71" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71)</f>
         <v>20</v>
       </c>
-      <c r="I71" s="1" t="str">
+      <c r="I71" s="0" t="str">
         <f aca="false">IF(AND($D71&gt;0,$H71=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B72" s="1" t="str">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B72" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="13" t="s">
         <v>1477</v>
       </c>
-      <c r="D72" s="1" t="n">
+      <c r="D72" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>10</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
         <v>5</v>
       </c>
-      <c r="F72" s="1" t="n">
+      <c r="F72" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
         <v>5</v>
       </c>
-      <c r="G72" s="1" t="n">
+      <c r="G72" s="0" t="n">
         <f aca="false">IF($D72=0,0,$E72/$D72)</f>
         <v>0.5</v>
       </c>
-      <c r="H72" s="1" t="n">
+      <c r="H72" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72)</f>
         <v>20</v>
       </c>
-      <c r="I72" s="1" t="str">
+      <c r="I72" s="0" t="str">
         <f aca="false">IF(AND($D72&gt;0,$H72=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B73" s="1" t="str">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B73" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="13" t="s">
         <v>1484</v>
       </c>
-      <c r="D73" s="1" t="n">
+      <c r="D73" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
         <v>1</v>
       </c>
-      <c r="F73" s="1" t="n">
+      <c r="F73" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
         <v>6</v>
       </c>
-      <c r="G73" s="1" t="n">
+      <c r="G73" s="0" t="n">
         <f aca="false">IF($D73=0,0,$E73/$D73)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="H73" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73)</f>
         <v>18</v>
       </c>
-      <c r="I73" s="1" t="str">
+      <c r="I73" s="0" t="str">
         <f aca="false">IF(AND($D73&gt;0,$H73=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B74" s="1" t="str">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B74" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D74" s="1" t="n">
+      <c r="C74" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D74" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
         <v>1</v>
       </c>
-      <c r="F74" s="1" t="n">
+      <c r="F74" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
         <v>4</v>
       </c>
-      <c r="G74" s="1" t="n">
+      <c r="G74" s="0" t="n">
         <f aca="false">IF($D74=0,0,$E74/$D74)</f>
         <v>0.2</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="H74" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74)</f>
         <v>6</v>
       </c>
-      <c r="I74" s="1" t="str">
+      <c r="I74" s="0" t="str">
         <f aca="false">IF(AND($D74&gt;0,$H74=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B75" s="1" t="str">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B75" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="13" t="s">
         <v>1481</v>
       </c>
-      <c r="D75" s="1" t="n">
+      <c r="D75" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
         <v>2</v>
       </c>
-      <c r="F75" s="1" t="n">
+      <c r="F75" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
         <v>5</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="G75" s="0" t="n">
         <f aca="false">IF($D75=0,0,$E75/$D75)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="H75" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75)</f>
         <v>17</v>
       </c>
-      <c r="I75" s="1" t="str">
+      <c r="I75" s="0" t="str">
         <f aca="false">IF(AND($D75&gt;0,$H75=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B76" s="1" t="str">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B76" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D76" s="1" t="n">
+      <c r="C76" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D76" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E76" s="1" t="n">
+      <c r="E76" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
         <v>6</v>
       </c>
-      <c r="F76" s="1" t="n">
+      <c r="F76" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
         <v>7</v>
       </c>
-      <c r="G76" s="1" t="n">
+      <c r="G76" s="0" t="n">
         <f aca="false">IF($D76=0,0,$E76/$D76)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="H76" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76)</f>
         <v>26</v>
       </c>
-      <c r="I76" s="1" t="str">
+      <c r="I76" s="0" t="str">
         <f aca="false">IF(AND($D76&gt;0,$H76=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B77" s="1" t="str">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B77" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D77" s="1" t="n">
+      <c r="C77" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D77" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>22</v>
       </c>
-      <c r="E77" s="1" t="n">
+      <c r="E77" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
         <v>11</v>
       </c>
-      <c r="F77" s="1" t="n">
+      <c r="F77" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
         <v>11</v>
       </c>
-      <c r="G77" s="1" t="n">
+      <c r="G77" s="0" t="n">
         <f aca="false">IF($D77=0,0,$E77/$D77)</f>
         <v>0.5</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="H77" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77)</f>
         <v>40</v>
       </c>
-      <c r="I77" s="1" t="str">
+      <c r="I77" s="0" t="str">
         <f aca="false">IF(AND($D77&gt;0,$H77=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B78" s="1" t="str">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B78" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="13" t="s">
         <v>1495</v>
       </c>
-      <c r="D78" s="1" t="n">
+      <c r="D78" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="E78" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
         <v>0</v>
       </c>
-      <c r="F78" s="1" t="n">
+      <c r="F78" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
         <v>0</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="G78" s="0" t="n">
         <f aca="false">IF($D78=0,0,$E78/$D78)</f>
         <v>0</v>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="H78" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78)</f>
         <v>11</v>
       </c>
-      <c r="I78" s="1" t="str">
+      <c r="I78" s="0" t="str">
         <f aca="false">IF(AND($D78&gt;0,$H78=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B79" s="1" t="str">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="13" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B79" s="0" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D79" s="1" t="n">
+      <c r="C79" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D79" s="0" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="E79" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
         <v>0</v>
       </c>
-      <c r="F79" s="1" t="n">
+      <c r="F79" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
         <v>0</v>
       </c>
-      <c r="G79" s="1" t="n">
+      <c r="G79" s="0" t="n">
         <f aca="false">IF($D79=0,0,$E79/$D79)</f>
         <v>0</v>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="H79" s="0" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79)</f>
         <v>20</v>
       </c>
-      <c r="I79" s="1" t="str">
+      <c r="I79" s="0" t="str">
         <f aca="false">IF(AND($D79&gt;0,$H79=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B80" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A80,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A80,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>28</v>
+      </c>
+      <c r="E80" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C80,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D80)</f>
+        <v>4</v>
+      </c>
+      <c r="F80" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C80,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D80)</f>
+        <v>24</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <f aca="false">IF($D80=0,0,$E80/$D80)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H80" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C80)</f>
+        <v>36</v>
+      </c>
+      <c r="I80" s="0" t="str">
+        <f aca="false">IF(AND($D80&gt;0,$H80=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B81" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A81,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A81,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E81" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C81,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D81)</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C81,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D81)</f>
+        <v>6</v>
+      </c>
+      <c r="G81" s="0" t="n">
+        <f aca="false">IF($D81=0,0,$E81/$D81)</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C81)</f>
+        <v>9</v>
+      </c>
+      <c r="I81" s="0" t="str">
+        <f aca="false">IF(AND($D81&gt;0,$H81=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B82" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A82,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A82,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E82" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C82,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D82)</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C82,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D82)</f>
+        <v>7</v>
+      </c>
+      <c r="G82" s="0" t="n">
+        <f aca="false">IF($D82=0,0,$E82/$D82)</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C82)</f>
+        <v>11</v>
+      </c>
+      <c r="I82" s="0" t="str">
+        <f aca="false">IF(AND($D82&gt;0,$H82=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B83" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A83,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A83,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>11</v>
+      </c>
+      <c r="E83" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C83,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D83)</f>
+        <v>2</v>
+      </c>
+      <c r="F83" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C83,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D83)</f>
+        <v>8</v>
+      </c>
+      <c r="G83" s="0" t="n">
+        <f aca="false">IF($D83=0,0,$E83/$D83)</f>
+        <v>0.181818181818182</v>
+      </c>
+      <c r="H83" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C83)</f>
+        <v>10</v>
+      </c>
+      <c r="I83" s="0" t="str">
+        <f aca="false">IF(AND($D83&gt;0,$H83=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B84" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A84,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A84,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>5</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C84,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D84)</f>
+        <v>2</v>
+      </c>
+      <c r="F84" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C84,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D84)</f>
+        <v>3</v>
+      </c>
+      <c r="G84" s="0" t="n">
+        <f aca="false">IF($D84=0,0,$E84/$D84)</f>
+        <v>0.4</v>
+      </c>
+      <c r="H84" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C84)</f>
+        <v>20</v>
+      </c>
+      <c r="I84" s="0" t="str">
+        <f aca="false">IF(AND($D84&gt;0,$H84=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B85" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A85,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A85,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E85" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C85,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D85)</f>
+        <v>4</v>
+      </c>
+      <c r="F85" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C85,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D85)</f>
+        <v>5</v>
+      </c>
+      <c r="G85" s="0" t="n">
+        <f aca="false">IF($D85=0,0,$E85/$D85)</f>
+        <v>0.444444444444444</v>
+      </c>
+      <c r="H85" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C85)</f>
+        <v>20</v>
+      </c>
+      <c r="I85" s="0" t="str">
+        <f aca="false">IF(AND($D85&gt;0,$H85=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B86" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A86,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D86" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A86,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E86" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C86,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D86)</f>
+        <v>1</v>
+      </c>
+      <c r="F86" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C86,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D86)</f>
+        <v>5</v>
+      </c>
+      <c r="G86" s="0" t="n">
+        <f aca="false">IF($D86=0,0,$E86/$D86)</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="H86" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C86)</f>
+        <v>18</v>
+      </c>
+      <c r="I86" s="0" t="str">
+        <f aca="false">IF(AND($D86&gt;0,$H86=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B87" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A87,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D87" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A87,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>7</v>
+      </c>
+      <c r="E87" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C87,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D87)</f>
+        <v>1</v>
+      </c>
+      <c r="F87" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C87,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D87)</f>
+        <v>5</v>
+      </c>
+      <c r="G87" s="0" t="n">
+        <f aca="false">IF($D87=0,0,$E87/$D87)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="H87" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C87)</f>
+        <v>6</v>
+      </c>
+      <c r="I87" s="0" t="str">
+        <f aca="false">IF(AND($D87&gt;0,$H87=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B88" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A88,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D88" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A88,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E88" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C88,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D88)</f>
+        <v>2</v>
+      </c>
+      <c r="F88" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C88,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D88)</f>
+        <v>4</v>
+      </c>
+      <c r="G88" s="0" t="n">
+        <f aca="false">IF($D88=0,0,$E88/$D88)</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H88" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C88)</f>
+        <v>17</v>
+      </c>
+      <c r="I88" s="0" t="str">
+        <f aca="false">IF(AND($D88&gt;0,$H88=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B89" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A89,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D89" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A89,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>13</v>
+      </c>
+      <c r="E89" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C89,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D89)</f>
+        <v>6</v>
+      </c>
+      <c r="F89" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C89,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D89)</f>
+        <v>7</v>
+      </c>
+      <c r="G89" s="0" t="n">
+        <f aca="false">IF($D89=0,0,$E89/$D89)</f>
+        <v>0.461538461538462</v>
+      </c>
+      <c r="H89" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C89)</f>
+        <v>26</v>
+      </c>
+      <c r="I89" s="0" t="str">
+        <f aca="false">IF(AND($D89&gt;0,$H89=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B90" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A90,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D90" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A90,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>21</v>
+      </c>
+      <c r="E90" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C90,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D90)</f>
+        <v>11</v>
+      </c>
+      <c r="F90" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C90,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D90)</f>
+        <v>10</v>
+      </c>
+      <c r="G90" s="0" t="n">
+        <f aca="false">IF($D90=0,0,$E90/$D90)</f>
+        <v>0.523809523809524</v>
+      </c>
+      <c r="H90" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C90)</f>
+        <v>40</v>
+      </c>
+      <c r="I90" s="0" t="str">
+        <f aca="false">IF(AND($D90&gt;0,$H90=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B91" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A91,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D91" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A91,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C91,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D91)</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C91,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D91)</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="0" t="n">
+        <f aca="false">IF($D91=0,0,$E91/$D91)</f>
+        <v>0</v>
+      </c>
+      <c r="H91" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C91)</f>
+        <v>11</v>
+      </c>
+      <c r="I91" s="0" t="str">
+        <f aca="false">IF(AND($D91&gt;0,$H91=0),"אין נתוני מועמדים לחישוב","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B92" s="0" t="str">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A92,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>2026-10-27</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D92" s="0" t="n">
+        <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A92,'סקרים לפי ערוץ'!$A:$A,0))</f>
+        <v>0</v>
+      </c>
+      <c r="E92" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C92,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D92)</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C92,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D92)</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="0" t="n">
+        <f aca="false">IF($D92=0,0,$E92/$D92)</f>
+        <v>0</v>
+      </c>
+      <c r="H92" s="0" t="n">
+        <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C92)</f>
+        <v>20</v>
+      </c>
+      <c r="I92" s="0" t="str">
+        <f aca="false">IF(AND($D92&gt;0,$H92=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>

--- a/party-comparison-updated-v83.xlsx
+++ b/party-comparison-updated-v83.xlsx
@@ -570,7 +570,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7583" uniqueCount="1858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7595" uniqueCount="1853">
   <si>
     <t xml:space="preserve">מפלגה</t>
   </si>
@@ -6823,6 +6823,15 @@
     <t xml:space="preserve">חסן אלנסאסרה </t>
   </si>
   <si>
+    <t xml:space="preserve">האיתם זחאלקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לפי הרשימה הרשמית שהוגשה לוועדת הבחירות המרכזית לכנסת ה-26, gov.il/he/pages/candidates-lists-26 (כפי שהועתקה ע"י המשתמש 28.10.2026). מגדר לפי השם.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איאס נאטור</t>
+  </si>
+  <si>
     <t xml:space="preserve">יעקב אשר</t>
   </si>
   <si>
@@ -7219,6 +7228,9 @@
     <t xml:space="preserve">חבר/ת כנסת מכהן/ת </t>
   </si>
   <si>
+    <t xml:space="preserve">איברהים אל טורי</t>
+  </si>
+  <si>
     <t xml:space="preserve">אריה מכלוף דרעי</t>
   </si>
   <si>
@@ -7369,393 +7381,19 @@
     <t xml:space="preserve">יצחק כ״ץ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ממוצע </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">מדגמים</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ממוצע</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 12, 13, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">כאן</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 14, i24</t>
-    </r>
+    <t xml:space="preserve">ממוצע 5 מדגמים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ממוצע: 12, 13, כאן, 14, i24</t>
   </si>
   <si>
     <t xml:space="preserve">מנדטים</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">מועמדים ידועים </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">סה</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">כ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">מועמדים ידועים (סה"כ)</t>
   </si>
   <si>
     <t xml:space="preserve">הערה</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">חדשות </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ש</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ס</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">רע</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">מ</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ביחד </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">בנט</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">לפיד</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ישר</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">המילואימניקים</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">הכלכלית</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">חדשות </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ערוץ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ערוץ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -7774,18 +7412,18 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="0"/>
     </font>
     <font>
@@ -7798,14 +7436,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="FreeSans"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="FreeSans"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
@@ -7846,13 +7484,13 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="FreeSans"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -7930,7 +7568,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7980,10 +7618,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -42860,7 +42494,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E264"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -45179,10 +44813,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>1480</v>
+        <v>1491</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>1662</v>
@@ -45196,10 +44830,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>1480</v>
+        <v>1491</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>1664</v>
@@ -45216,7 +44850,7 @@
         <v>1480</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>1665</v>
@@ -45225,7 +44859,7 @@
         <v>1456</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45233,16 +44867,16 @@
         <v>1480</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C142" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E142" s="3" t="s">
         <v>1666</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45250,16 +44884,16 @@
         <v>1480</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45267,16 +44901,16 @@
         <v>1480</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45284,16 +44918,16 @@
         <v>1480</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45301,16 +44935,16 @@
         <v>1480</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45318,44 +44952,50 @@
         <v>1480</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>1456</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>1666</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>1456</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>1666</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45363,13 +45003,13 @@
         <v>1488</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45377,13 +45017,13 @@
         <v>1488</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45391,13 +45031,13 @@
         <v>1488</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45405,13 +45045,13 @@
         <v>1488</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45419,10 +45059,10 @@
         <v>1488</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>1456</v>
@@ -45433,13 +45073,13 @@
         <v>1488</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45447,13 +45087,13 @@
         <v>1488</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45461,10 +45101,10 @@
         <v>1488</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>1455</v>
@@ -45475,10 +45115,10 @@
         <v>1488</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>1455</v>
@@ -45489,13 +45129,13 @@
         <v>1488</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45503,13 +45143,13 @@
         <v>1488</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45517,13 +45157,13 @@
         <v>1488</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45531,13 +45171,13 @@
         <v>1488</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45545,10 +45185,10 @@
         <v>1488</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>1455</v>
@@ -45559,13 +45199,13 @@
         <v>1488</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45573,13 +45213,13 @@
         <v>1488</v>
       </c>
       <c r="B165" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45587,13 +45227,13 @@
         <v>1488</v>
       </c>
       <c r="B166" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45601,10 +45241,10 @@
         <v>1488</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>1456</v>
@@ -45615,10 +45255,10 @@
         <v>1488</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>1455</v>
@@ -45629,10 +45269,10 @@
         <v>1488</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>1456</v>
@@ -45643,13 +45283,13 @@
         <v>1488</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45657,13 +45297,13 @@
         <v>1488</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45671,13 +45311,13 @@
         <v>1488</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45685,13 +45325,13 @@
         <v>1488</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45699,13 +45339,13 @@
         <v>1488</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45713,13 +45353,13 @@
         <v>1488</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45727,10 +45367,10 @@
         <v>1488</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>1456</v>
@@ -45741,10 +45381,10 @@
         <v>1488</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>1455</v>
@@ -45755,10 +45395,10 @@
         <v>1488</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>1456</v>
@@ -45769,10 +45409,10 @@
         <v>1488</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>1455</v>
@@ -45783,10 +45423,10 @@
         <v>1488</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>1456</v>
@@ -45797,10 +45437,10 @@
         <v>1488</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>1455</v>
@@ -45811,10 +45451,10 @@
         <v>1488</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>1456</v>
@@ -45825,10 +45465,10 @@
         <v>1488</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>1455</v>
@@ -45839,10 +45479,10 @@
         <v>1488</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>1456</v>
@@ -45853,10 +45493,10 @@
         <v>1488</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>1455</v>
@@ -45867,10 +45507,10 @@
         <v>1488</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>1456</v>
@@ -45881,47 +45521,41 @@
         <v>1488</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>1456</v>
-      </c>
-      <c r="E188" s="3" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>1714</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>1456</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45929,16 +45563,16 @@
         <v>1490</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>1715</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45946,16 +45580,16 @@
         <v>1490</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C191" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E191" s="3" t="s">
         <v>1716</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45963,16 +45597,16 @@
         <v>1490</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45980,16 +45614,16 @@
         <v>1490</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45997,16 +45631,16 @@
         <v>1490</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46014,16 +45648,16 @@
         <v>1490</v>
       </c>
       <c r="B195" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46031,16 +45665,16 @@
         <v>1490</v>
       </c>
       <c r="B196" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46048,16 +45682,16 @@
         <v>1490</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46065,16 +45699,16 @@
         <v>1490</v>
       </c>
       <c r="B198" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46082,16 +45716,16 @@
         <v>1490</v>
       </c>
       <c r="B199" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46099,16 +45733,16 @@
         <v>1490</v>
       </c>
       <c r="B200" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46116,16 +45750,16 @@
         <v>1490</v>
       </c>
       <c r="B201" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46133,16 +45767,16 @@
         <v>1490</v>
       </c>
       <c r="B202" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46150,16 +45784,16 @@
         <v>1490</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46167,16 +45801,16 @@
         <v>1490</v>
       </c>
       <c r="B204" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46184,16 +45818,16 @@
         <v>1490</v>
       </c>
       <c r="B205" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46201,16 +45835,16 @@
         <v>1490</v>
       </c>
       <c r="B206" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46218,50 +45852,50 @@
         <v>1490</v>
       </c>
       <c r="B207" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B208" s="1" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>1734</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B209" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>1735</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>1734</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46269,16 +45903,16 @@
         <v>1492</v>
       </c>
       <c r="B210" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>1736</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46286,16 +45920,16 @@
         <v>1492</v>
       </c>
       <c r="B211" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C211" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E211" s="3" t="s">
         <v>1737</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46303,50 +45937,50 @@
         <v>1492</v>
       </c>
       <c r="B212" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="B213" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>452</v>
+        <v>1740</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>1625</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="B214" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>1625</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46354,10 +45988,10 @@
         <v>1498</v>
       </c>
       <c r="B215" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>1740</v>
+        <v>452</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>1456</v>
@@ -46371,13 +46005,13 @@
         <v>1498</v>
       </c>
       <c r="B216" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>1625</v>
@@ -46385,27 +46019,27 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>1481</v>
+        <v>1498</v>
       </c>
       <c r="B217" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>1743</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>1481</v>
+        <v>1498</v>
       </c>
       <c r="B218" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>1744</v>
@@ -46414,7 +46048,7 @@
         <v>1455</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>1745</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46422,16 +46056,16 @@
         <v>1481</v>
       </c>
       <c r="B219" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C219" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E219" s="3" t="s">
         <v>1746</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46439,16 +46073,16 @@
         <v>1481</v>
       </c>
       <c r="B220" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C220" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E220" s="3" t="s">
         <v>1748</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46456,16 +46090,16 @@
         <v>1481</v>
       </c>
       <c r="B221" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>1749</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46473,16 +46107,16 @@
         <v>1481</v>
       </c>
       <c r="B222" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C222" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E222" s="3" t="s">
         <v>1750</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46490,16 +46124,16 @@
         <v>1481</v>
       </c>
       <c r="B223" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46507,16 +46141,16 @@
         <v>1481</v>
       </c>
       <c r="B224" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46524,16 +46158,16 @@
         <v>1481</v>
       </c>
       <c r="B225" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46541,7 +46175,7 @@
         <v>1481</v>
       </c>
       <c r="B226" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>1755</v>
@@ -46550,7 +46184,7 @@
         <v>1456</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46558,13 +46192,16 @@
         <v>1481</v>
       </c>
       <c r="B227" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>1756</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>1456</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>1757</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46572,13 +46209,16 @@
         <v>1481</v>
       </c>
       <c r="B228" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>1456</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>1750</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46586,13 +46226,13 @@
         <v>1481</v>
       </c>
       <c r="B229" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46600,10 +46240,10 @@
         <v>1481</v>
       </c>
       <c r="B230" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>1456</v>
@@ -46614,13 +46254,13 @@
         <v>1481</v>
       </c>
       <c r="B231" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46628,10 +46268,10 @@
         <v>1481</v>
       </c>
       <c r="B232" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>1456</v>
@@ -46642,10 +46282,10 @@
         <v>1481</v>
       </c>
       <c r="B233" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>1456</v>
@@ -46653,36 +46293,30 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>1495</v>
+        <v>1481</v>
       </c>
       <c r="B234" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>1456</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>1495</v>
+        <v>1481</v>
       </c>
       <c r="B235" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>1765</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>1456</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46690,16 +46324,16 @@
         <v>1495</v>
       </c>
       <c r="B236" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C236" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E236" s="3" t="s">
         <v>1767</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46707,16 +46341,16 @@
         <v>1495</v>
       </c>
       <c r="B237" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C237" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E237" s="3" t="s">
         <v>1769</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46724,16 +46358,16 @@
         <v>1495</v>
       </c>
       <c r="B238" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>1455</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46741,16 +46375,16 @@
         <v>1495</v>
       </c>
       <c r="B239" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C239" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E239" s="3" t="s">
         <v>1773</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46758,16 +46392,16 @@
         <v>1495</v>
       </c>
       <c r="B240" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C240" s="3" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E240" s="3" t="s">
         <v>1775</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46775,16 +46409,16 @@
         <v>1495</v>
       </c>
       <c r="B241" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C241" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E241" s="3" t="s">
         <v>1777</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>1778</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46792,16 +46426,16 @@
         <v>1495</v>
       </c>
       <c r="B242" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C242" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E242" s="3" t="s">
         <v>1779</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46809,16 +46443,16 @@
         <v>1495</v>
       </c>
       <c r="B243" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C243" s="3" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E243" s="3" t="s">
         <v>1781</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46826,50 +46460,50 @@
         <v>1495</v>
       </c>
       <c r="B244" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C244" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E244" s="3" t="s">
         <v>1783</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>1784</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>1482</v>
+        <v>1495</v>
       </c>
       <c r="B245" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C245" s="3" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E245" s="3" t="s">
         <v>1785</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>1482</v>
+        <v>1495</v>
       </c>
       <c r="B246" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C246" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E246" s="3" t="s">
         <v>1787</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46877,16 +46511,16 @@
         <v>1482</v>
       </c>
       <c r="B247" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C247" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E247" s="3" t="s">
         <v>1789</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E247" s="3" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46894,7 +46528,7 @@
         <v>1482</v>
       </c>
       <c r="B248" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>1790</v>
@@ -46903,7 +46537,7 @@
         <v>1456</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>1786</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46911,16 +46545,16 @@
         <v>1482</v>
       </c>
       <c r="B249" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46928,58 +46562,58 @@
         <v>1482</v>
       </c>
       <c r="B250" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>1793</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B251" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>1794</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>1795</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B252" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C252" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E252" s="3" t="s">
         <v>1796</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E252" s="3" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B253" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>1797</v>
@@ -46988,7 +46622,7 @@
         <v>1456</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>1795</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46996,7 +46630,7 @@
         <v>1479</v>
       </c>
       <c r="B254" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>1798</v>
@@ -47005,7 +46639,7 @@
         <v>1456</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47013,16 +46647,16 @@
         <v>1479</v>
       </c>
       <c r="B255" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C255" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E255" s="3" t="s">
         <v>1799</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47030,16 +46664,16 @@
         <v>1479</v>
       </c>
       <c r="B256" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47047,16 +46681,16 @@
         <v>1479</v>
       </c>
       <c r="B257" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47064,16 +46698,16 @@
         <v>1479</v>
       </c>
       <c r="B258" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47081,13 +46715,16 @@
         <v>1479</v>
       </c>
       <c r="B259" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>1456</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>1799</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47095,13 +46732,16 @@
         <v>1479</v>
       </c>
       <c r="B260" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>1456</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>1799</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47109,12 +46749,57 @@
         <v>1479</v>
       </c>
       <c r="B261" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B262" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B263" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B264" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C261" s="3" t="s">
-        <v>1805</v>
-      </c>
-      <c r="D261" s="3" t="s">
+      <c r="C264" s="3" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D264" s="3" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -47156,7 +46841,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>1472</v>
@@ -47165,19 +46850,19 @@
         <v>1473</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47201,7 +46886,7 @@
         <v>0.148148148148148</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>32</v>
@@ -47235,7 +46920,7 @@
         <v>0.523809523809524</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>0</v>
@@ -47269,7 +46954,7 @@
         <v>0.461538461538462</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>24</v>
@@ -47303,7 +46988,7 @@
         <v>0.444444444444444</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>4</v>
@@ -47337,7 +47022,7 @@
         <v>0.285714285714286</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>6</v>
@@ -47371,7 +47056,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>11</v>
@@ -47405,7 +47090,7 @@
         <v>0.333333333333333</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>6</v>
@@ -47439,7 +47124,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>7</v>
@@ -47466,14 +47151,14 @@
       </c>
       <c r="D10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A10,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B10)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="n">
         <f aca="false">IF(B10=0,0,C10/B10)</f>
         <v>0.181818181818182</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>5</v>
@@ -47507,7 +47192,7 @@
         <v>0.166666666666667</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>7</v>
@@ -47534,14 +47219,14 @@
       </c>
       <c r="D12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,A12,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;B12)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="n">
         <f aca="false">IF(B12=0,0,C12/B12)</f>
         <v>0.142857142857143</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5</v>
@@ -47575,7 +47260,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>0</v>
@@ -47609,7 +47294,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>0</v>
@@ -47643,7 +47328,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>0</v>
@@ -47658,7 +47343,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="B16" s="1" t="n">
         <f aca="false">SUM(B2:B14)</f>
@@ -47670,7 +47355,7 @@
       </c>
       <c r="D16" s="1" t="n">
         <f aca="false">SUM(D2:D14)</f>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="n">
         <f aca="false">IF(B16=0,0,C16/B16)</f>
@@ -47711,16 +47396,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1474</v>
@@ -47767,13 +47452,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>27</v>
@@ -47820,13 +47505,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>27</v>
@@ -47873,13 +47558,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>1836</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>1832</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>27</v>
@@ -47926,13 +47611,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>31</v>
@@ -47979,13 +47664,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>27</v>
@@ -48032,13 +47717,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>25</v>
@@ -48083,56 +47768,56 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>1832</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>1845</v>
-      </c>
-      <c r="E8" s="0" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -48156,3307 +47841,3307 @@
   <dimension ref="A1:I92"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>1827</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C1" s="13" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>1846</v>
-      </c>
-      <c r="E1" s="13" t="s">
+      <c r="D1" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1472</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="3" t="s">
         <v>1473</v>
       </c>
-      <c r="G1" s="13" t="s">
-        <v>1807</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>1847</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B2" s="0" t="str">
+      <c r="G1" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B2" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A2,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D2)</f>
         <v>23</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <f aca="false">IF($D2=0,0,$E2/$D2)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C2)</f>
         <v>36</v>
       </c>
-      <c r="I2" s="0" t="str">
+      <c r="I2" s="1" t="str">
         <f aca="false">IF(AND($D2&gt;0,$H2=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B3" s="0" t="str">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B3" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A3,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D3)</f>
         <v>6</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <f aca="false">IF($D3=0,0,$E3/$D3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C3)</f>
         <v>9</v>
       </c>
-      <c r="I3" s="0" t="str">
+      <c r="I3" s="1" t="str">
         <f aca="false">IF(AND($D3&gt;0,$H3=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B4" s="0" t="str">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B4" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A4,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D4)</f>
         <v>7</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <f aca="false">IF($D4=0,0,$E4/$D4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C4)</f>
         <v>11</v>
       </c>
-      <c r="I4" s="0" t="str">
+      <c r="I4" s="1" t="str">
         <f aca="false">IF(AND($D4&gt;0,$H4=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B5" s="0" t="str">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B5" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A5,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>12</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D5)</f>
-        <v>8</v>
-      </c>
-      <c r="G5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <f aca="false">IF($D5=0,0,$E5/$D5)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C5)</f>
-        <v>10</v>
-      </c>
-      <c r="I5" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="str">
         <f aca="false">IF(AND($D5&gt;0,$H5=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B6" s="0" t="str">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B6" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A6,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
         <v>2</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D6)</f>
         <v>5</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <f aca="false">IF($D6=0,0,$E6/$D6)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C6)</f>
         <v>20</v>
       </c>
-      <c r="I6" s="0" t="str">
+      <c r="I6" s="1" t="str">
         <f aca="false">IF(AND($D6&gt;0,$H6=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B7" s="0" t="str">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B7" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A7,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
         <v>4</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D7)</f>
         <v>5</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <f aca="false">IF($D7=0,0,$E7/$D7)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C7)</f>
         <v>20</v>
       </c>
-      <c r="I7" s="0" t="str">
+      <c r="I7" s="1" t="str">
         <f aca="false">IF(AND($D7&gt;0,$H7=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B8" s="0" t="str">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B8" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A8,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D8)</f>
         <v>5</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <f aca="false">IF($D8=0,0,$E8/$D8)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C8)</f>
         <v>18</v>
       </c>
-      <c r="I8" s="0" t="str">
+      <c r="I8" s="1" t="str">
         <f aca="false">IF(AND($D8&gt;0,$H8=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B9" s="0" t="str">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B9" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A9,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
         <v>1</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D9)</f>
-        <v>5</v>
-      </c>
-      <c r="G9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <f aca="false">IF($D9=0,0,$E9/$D9)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C9)</f>
-        <v>6</v>
-      </c>
-      <c r="I9" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I9" s="1" t="str">
         <f aca="false">IF(AND($D9&gt;0,$H9=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B10" s="0" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B10" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A10,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D10)</f>
         <v>4</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <f aca="false">IF($D10=0,0,$E10/$D10)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C10)</f>
         <v>17</v>
       </c>
-      <c r="I10" s="0" t="str">
+      <c r="I10" s="1" t="str">
         <f aca="false">IF(AND($D10&gt;0,$H10=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B11" s="0" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B11" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A11,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>12</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
         <v>6</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <f aca="false">IF($D11=0,0,$E11/$D11)</f>
         <v>0.5</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C11)</f>
         <v>26</v>
       </c>
-      <c r="I11" s="0" t="str">
+      <c r="I11" s="1" t="str">
         <f aca="false">IF(AND($D11&gt;0,$H11=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B12" s="0" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B12" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A12,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
         <v>11</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D12)</f>
         <v>10</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <f aca="false">IF($D12=0,0,$E12/$D12)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C12)</f>
         <v>40</v>
       </c>
-      <c r="I12" s="0" t="str">
+      <c r="I12" s="1" t="str">
         <f aca="false">IF(AND($D12&gt;0,$H12=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B13" s="0" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B13" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A13,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <f aca="false">IF($D13=0,0,$E13/$D13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C13)</f>
         <v>11</v>
       </c>
-      <c r="I13" s="0" t="str">
+      <c r="I13" s="1" t="str">
         <f aca="false">IF(AND($D13&gt;0,$H13=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B14" s="0" t="str">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B14" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A14,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <f aca="false">IF($D14=0,0,$E14/$D14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C14)</f>
         <v>20</v>
       </c>
-      <c r="I14" s="0" t="str">
+      <c r="I14" s="1" t="str">
         <f aca="false">IF(AND($D14&gt;0,$H14=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B15" s="0" t="str">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B15" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A15,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
         <v>4</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D15)</f>
         <v>23</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <f aca="false">IF($D15=0,0,$E15/$D15)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C15)</f>
         <v>36</v>
       </c>
-      <c r="I15" s="0" t="str">
+      <c r="I15" s="1" t="str">
         <f aca="false">IF(AND($D15&gt;0,$H15=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B16" s="0" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B16" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A16,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D16)</f>
         <v>6</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <f aca="false">IF($D16=0,0,$E16/$D16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C16)</f>
         <v>9</v>
       </c>
-      <c r="I16" s="0" t="str">
+      <c r="I16" s="1" t="str">
         <f aca="false">IF(AND($D16&gt;0,$H16=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B17" s="0" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B17" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A17,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D17)</f>
         <v>6</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <f aca="false">IF($D17=0,0,$E17/$D17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C17)</f>
         <v>11</v>
       </c>
-      <c r="I17" s="0" t="str">
+      <c r="I17" s="1" t="str">
         <f aca="false">IF(AND($D17&gt;0,$H17=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B18" s="0" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B18" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A18,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
         <v>2</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D18)</f>
-        <v>8</v>
-      </c>
-      <c r="G18" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <f aca="false">IF($D18=0,0,$E18/$D18)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C18)</f>
-        <v>10</v>
-      </c>
-      <c r="I18" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I18" s="1" t="str">
         <f aca="false">IF(AND($D18&gt;0,$H18=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B19" s="0" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B19" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A19,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
         <v>2</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D19)</f>
         <v>5</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <f aca="false">IF($D19=0,0,$E19/$D19)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C19)</f>
         <v>20</v>
       </c>
-      <c r="I19" s="0" t="str">
+      <c r="I19" s="1" t="str">
         <f aca="false">IF(AND($D19&gt;0,$H19=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B20" s="0" t="str">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B20" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A20,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
         <v>4</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D20)</f>
         <v>5</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <f aca="false">IF($D20=0,0,$E20/$D20)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C20)</f>
         <v>20</v>
       </c>
-      <c r="I20" s="0" t="str">
+      <c r="I20" s="1" t="str">
         <f aca="false">IF(AND($D20&gt;0,$H20=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B21" s="0" t="str">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B21" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A21,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D21)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <f aca="false">IF($D21=0,0,$E21/$D21)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C21)</f>
         <v>18</v>
       </c>
-      <c r="I21" s="0" t="str">
+      <c r="I21" s="1" t="str">
         <f aca="false">IF(AND($D21&gt;0,$H21=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B22" s="0" t="str">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B22" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="C22" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A22,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
         <v>1</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D22)</f>
-        <v>5</v>
-      </c>
-      <c r="G22" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <f aca="false">IF($D22=0,0,$E22/$D22)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C22)</f>
-        <v>6</v>
-      </c>
-      <c r="I22" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I22" s="1" t="str">
         <f aca="false">IF(AND($D22&gt;0,$H22=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B23" s="0" t="str">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B23" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A23,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D23)</f>
         <v>4</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="1" t="n">
         <f aca="false">IF($D23=0,0,$E23/$D23)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C23)</f>
         <v>17</v>
       </c>
-      <c r="I23" s="0" t="str">
+      <c r="I23" s="1" t="str">
         <f aca="false">IF(AND($D23&gt;0,$H23=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B24" s="0" t="str">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B24" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D24" s="0" t="n">
+      <c r="C24" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D24" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A24,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
         <v>6</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D24)</f>
         <v>7</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="1" t="n">
         <f aca="false">IF($D24=0,0,$E24/$D24)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C24)</f>
         <v>26</v>
       </c>
-      <c r="I24" s="0" t="str">
+      <c r="I24" s="1" t="str">
         <f aca="false">IF(AND($D24&gt;0,$H24=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B25" s="0" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B25" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D25" s="0" t="n">
+      <c r="C25" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D25" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A25,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>22</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
         <v>11</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D25)</f>
         <v>11</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="1" t="n">
         <f aca="false">IF($D25=0,0,$E25/$D25)</f>
         <v>0.5</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C25)</f>
         <v>40</v>
       </c>
-      <c r="I25" s="0" t="str">
+      <c r="I25" s="1" t="str">
         <f aca="false">IF(AND($D25&gt;0,$H25=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B26" s="0" t="str">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B26" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A26,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D26)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="1" t="n">
         <f aca="false">IF($D26=0,0,$E26/$D26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C26)</f>
         <v>11</v>
       </c>
-      <c r="I26" s="0" t="str">
+      <c r="I26" s="1" t="str">
         <f aca="false">IF(AND($D26&gt;0,$H26=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B27" s="0" t="str">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B27" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D27" s="0" t="n">
+      <c r="C27" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D27" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A27,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D27)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27" s="1" t="n">
         <f aca="false">IF($D27=0,0,$E27/$D27)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C27)</f>
         <v>20</v>
       </c>
-      <c r="I27" s="0" t="str">
+      <c r="I27" s="1" t="str">
         <f aca="false">IF(AND($D27&gt;0,$H27=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B28" s="0" t="str">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B28" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A28,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D28)</f>
         <v>23</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <f aca="false">IF($D28=0,0,$E28/$D28)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C28)</f>
         <v>36</v>
       </c>
-      <c r="I28" s="0" t="str">
+      <c r="I28" s="1" t="str">
         <f aca="false">IF(AND($D28&gt;0,$H28=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B29" s="0" t="str">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B29" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A29,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D29)</f>
         <v>6</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="1" t="n">
         <f aca="false">IF($D29=0,0,$E29/$D29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C29)</f>
         <v>9</v>
       </c>
-      <c r="I29" s="0" t="str">
+      <c r="I29" s="1" t="str">
         <f aca="false">IF(AND($D29&gt;0,$H29=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B30" s="0" t="str">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B30" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D30" s="0" t="n">
+      <c r="C30" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D30" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A30,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D30)</f>
         <v>6</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="1" t="n">
         <f aca="false">IF($D30=0,0,$E30/$D30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C30)</f>
         <v>11</v>
       </c>
-      <c r="I30" s="0" t="str">
+      <c r="I30" s="1" t="str">
         <f aca="false">IF(AND($D30&gt;0,$H30=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B31" s="0" t="str">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B31" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A31,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
         <v>2</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D31)</f>
-        <v>8</v>
-      </c>
-      <c r="G31" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <f aca="false">IF($D31=0,0,$E31/$D31)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C31)</f>
-        <v>10</v>
-      </c>
-      <c r="I31" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I31" s="1" t="str">
         <f aca="false">IF(AND($D31&gt;0,$H31=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B32" s="0" t="str">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B32" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A32,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>8</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
         <v>2</v>
       </c>
-      <c r="F32" s="0" t="n">
+      <c r="F32" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D32)</f>
         <v>6</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32" s="1" t="n">
         <f aca="false">IF($D32=0,0,$E32/$D32)</f>
         <v>0.25</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C32)</f>
         <v>20</v>
       </c>
-      <c r="I32" s="0" t="str">
+      <c r="I32" s="1" t="str">
         <f aca="false">IF(AND($D32&gt;0,$H32=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B33" s="0" t="str">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B33" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A33,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
         <v>4</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D33)</f>
         <v>5</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="1" t="n">
         <f aca="false">IF($D33=0,0,$E33/$D33)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C33)</f>
         <v>20</v>
       </c>
-      <c r="I33" s="0" t="str">
+      <c r="I33" s="1" t="str">
         <f aca="false">IF(AND($D33&gt;0,$H33=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B34" s="0" t="str">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B34" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A34,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D34)</f>
         <v>5</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <f aca="false">IF($D34=0,0,$E34/$D34)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C34)</f>
         <v>18</v>
       </c>
-      <c r="I34" s="0" t="str">
+      <c r="I34" s="1" t="str">
         <f aca="false">IF(AND($D34&gt;0,$H34=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B35" s="0" t="str">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B35" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D35" s="0" t="n">
+      <c r="C35" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A35,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
         <v>1</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D35)</f>
-        <v>5</v>
-      </c>
-      <c r="G35" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <f aca="false">IF($D35=0,0,$E35/$D35)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C35)</f>
-        <v>6</v>
-      </c>
-      <c r="I35" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I35" s="1" t="str">
         <f aca="false">IF(AND($D35&gt;0,$H35=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B36" s="0" t="str">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B36" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A36,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
         <v>2</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D36)</f>
         <v>4</v>
       </c>
-      <c r="G36" s="0" t="n">
+      <c r="G36" s="1" t="n">
         <f aca="false">IF($D36=0,0,$E36/$D36)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H36" s="0" t="n">
+      <c r="H36" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C36)</f>
         <v>17</v>
       </c>
-      <c r="I36" s="0" t="str">
+      <c r="I36" s="1" t="str">
         <f aca="false">IF(AND($D36&gt;0,$H36=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B37" s="0" t="str">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B37" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D37" s="0" t="n">
+      <c r="C37" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D37" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A37,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
         <v>6</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D37)</f>
         <v>7</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="1" t="n">
         <f aca="false">IF($D37=0,0,$E37/$D37)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C37)</f>
         <v>26</v>
       </c>
-      <c r="I37" s="0" t="str">
+      <c r="I37" s="1" t="str">
         <f aca="false">IF(AND($D37&gt;0,$H37=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B38" s="0" t="str">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B38" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D38" s="0" t="n">
+      <c r="C38" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D38" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A38,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
         <v>11</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D38)</f>
         <v>10</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="1" t="n">
         <f aca="false">IF($D38=0,0,$E38/$D38)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C38)</f>
         <v>40</v>
       </c>
-      <c r="I38" s="0" t="str">
+      <c r="I38" s="1" t="str">
         <f aca="false">IF(AND($D38&gt;0,$H38=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B39" s="0" t="str">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B39" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A39,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D39)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="1" t="n">
         <f aca="false">IF($D39=0,0,$E39/$D39)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C39)</f>
         <v>11</v>
       </c>
-      <c r="I39" s="0" t="str">
+      <c r="I39" s="1" t="str">
         <f aca="false">IF(AND($D39&gt;0,$H39=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B40" s="0" t="str">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B40" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D40" s="0" t="n">
+      <c r="C40" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D40" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A40,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="1" t="n">
         <f aca="false">IF($D40=0,0,$E40/$D40)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C40)</f>
         <v>20</v>
       </c>
-      <c r="I40" s="0" t="str">
+      <c r="I40" s="1" t="str">
         <f aca="false">IF(AND($D40&gt;0,$H40=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B41" s="0" t="str">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B41" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A41,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>31</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
         <v>4</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D41)</f>
         <v>27</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G41" s="1" t="n">
         <f aca="false">IF($D41=0,0,$E41/$D41)</f>
         <v>0.129032258064516</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C41)</f>
         <v>36</v>
       </c>
-      <c r="I41" s="0" t="str">
+      <c r="I41" s="1" t="str">
         <f aca="false">IF(AND($D41&gt;0,$H41=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B42" s="0" t="str">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B42" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A42,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="0" t="n">
+      <c r="F42" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D42)</f>
         <v>7</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="1" t="n">
         <f aca="false">IF($D42=0,0,$E42/$D42)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C42)</f>
         <v>9</v>
       </c>
-      <c r="I42" s="0" t="str">
+      <c r="I42" s="1" t="str">
         <f aca="false">IF(AND($D42&gt;0,$H42=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B43" s="0" t="str">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B43" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D43" s="0" t="n">
+      <c r="C43" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D43" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A43,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>10</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="0" t="n">
+      <c r="F43" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D43)</f>
         <v>10</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="1" t="n">
         <f aca="false">IF($D43=0,0,$E43/$D43)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C43)</f>
         <v>11</v>
       </c>
-      <c r="I43" s="0" t="str">
+      <c r="I43" s="1" t="str">
         <f aca="false">IF(AND($D43&gt;0,$H43=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B44" s="0" t="str">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B44" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A44,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
         <v>2</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D44)</f>
-        <v>8</v>
-      </c>
-      <c r="G44" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <f aca="false">IF($D44=0,0,$E44/$D44)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C44)</f>
-        <v>10</v>
-      </c>
-      <c r="I44" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I44" s="1" t="str">
         <f aca="false">IF(AND($D44&gt;0,$H44=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B45" s="0" t="str">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B45" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A45,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="0" t="n">
+      <c r="F45" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D45)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="1" t="n">
         <f aca="false">IF($D45=0,0,$E45/$D45)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C45)</f>
         <v>20</v>
       </c>
-      <c r="I45" s="0" t="str">
+      <c r="I45" s="1" t="str">
         <f aca="false">IF(AND($D45&gt;0,$H45=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B46" s="0" t="str">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B46" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D46" s="0" t="n">
+      <c r="D46" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A46,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
         <v>4</v>
       </c>
-      <c r="F46" s="0" t="n">
+      <c r="F46" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D46)</f>
         <v>5</v>
       </c>
-      <c r="G46" s="0" t="n">
+      <c r="G46" s="1" t="n">
         <f aca="false">IF($D46=0,0,$E46/$D46)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H46" s="0" t="n">
+      <c r="H46" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C46)</f>
         <v>20</v>
       </c>
-      <c r="I46" s="0" t="str">
+      <c r="I46" s="1" t="str">
         <f aca="false">IF(AND($D46&gt;0,$H46=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B47" s="0" t="str">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B47" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D47" s="0" t="n">
+      <c r="D47" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A47,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
         <v>1</v>
       </c>
-      <c r="F47" s="0" t="n">
+      <c r="F47" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D47)</f>
         <v>6</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="1" t="n">
         <f aca="false">IF($D47=0,0,$E47/$D47)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C47)</f>
         <v>18</v>
       </c>
-      <c r="I47" s="0" t="str">
+      <c r="I47" s="1" t="str">
         <f aca="false">IF(AND($D47&gt;0,$H47=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B48" s="0" t="str">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B48" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D48" s="0" t="n">
+      <c r="C48" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A48,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
         <v>1</v>
       </c>
-      <c r="F48" s="0" t="n">
+      <c r="F48" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D48)</f>
-        <v>5</v>
-      </c>
-      <c r="G48" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <f aca="false">IF($D48=0,0,$E48/$D48)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C48)</f>
-        <v>6</v>
-      </c>
-      <c r="I48" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I48" s="1" t="str">
         <f aca="false">IF(AND($D48&gt;0,$H48=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B49" s="0" t="str">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B49" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D49" s="0" t="n">
+      <c r="D49" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A49,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
         <v>2</v>
       </c>
-      <c r="F49" s="0" t="n">
+      <c r="F49" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D49)</f>
         <v>5</v>
       </c>
-      <c r="G49" s="0" t="n">
+      <c r="G49" s="1" t="n">
         <f aca="false">IF($D49=0,0,$E49/$D49)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C49)</f>
         <v>17</v>
       </c>
-      <c r="I49" s="0" t="str">
+      <c r="I49" s="1" t="str">
         <f aca="false">IF(AND($D49&gt;0,$H49=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B50" s="0" t="str">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B50" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D50" s="0" t="n">
+      <c r="C50" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A50,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
         <v>6</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D50)</f>
         <v>5</v>
       </c>
-      <c r="G50" s="0" t="n">
+      <c r="G50" s="1" t="n">
         <f aca="false">IF($D50=0,0,$E50/$D50)</f>
         <v>0.545454545454545</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C50)</f>
         <v>26</v>
       </c>
-      <c r="I50" s="0" t="str">
+      <c r="I50" s="1" t="str">
         <f aca="false">IF(AND($D50&gt;0,$H50=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B51" s="0" t="str">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B51" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D51" s="0" t="n">
+      <c r="C51" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A51,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>20</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
         <v>10</v>
       </c>
-      <c r="F51" s="0" t="n">
+      <c r="F51" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D51)</f>
         <v>10</v>
       </c>
-      <c r="G51" s="0" t="n">
+      <c r="G51" s="1" t="n">
         <f aca="false">IF($D51=0,0,$E51/$D51)</f>
         <v>0.5</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C51)</f>
         <v>40</v>
       </c>
-      <c r="I51" s="0" t="str">
+      <c r="I51" s="1" t="str">
         <f aca="false">IF(AND($D51&gt;0,$H51=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B52" s="0" t="str">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B52" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A52,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
         <v>0</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D52)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <f aca="false">IF($D52=0,0,$E52/$D52)</f>
         <v>0</v>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C52)</f>
         <v>11</v>
       </c>
-      <c r="I52" s="0" t="str">
+      <c r="I52" s="1" t="str">
         <f aca="false">IF(AND($D52&gt;0,$H52=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B53" s="0" t="str">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B53" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D53" s="0" t="n">
+      <c r="C53" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A53,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
         <v>0</v>
       </c>
-      <c r="F53" s="0" t="n">
+      <c r="F53" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D53)</f>
         <v>0</v>
       </c>
-      <c r="G53" s="0" t="n">
+      <c r="G53" s="1" t="n">
         <f aca="false">IF($D53=0,0,$E53/$D53)</f>
         <v>0</v>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C53)</f>
         <v>20</v>
       </c>
-      <c r="I53" s="0" t="str">
+      <c r="I53" s="1" t="str">
         <f aca="false">IF(AND($D53&gt;0,$H53=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B54" s="0" t="str">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B54" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A54,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>27</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
         <v>4</v>
       </c>
-      <c r="F54" s="0" t="n">
+      <c r="F54" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D54)</f>
         <v>23</v>
       </c>
-      <c r="G54" s="0" t="n">
+      <c r="G54" s="1" t="n">
         <f aca="false">IF($D54=0,0,$E54/$D54)</f>
         <v>0.148148148148148</v>
       </c>
-      <c r="H54" s="0" t="n">
+      <c r="H54" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C54)</f>
         <v>36</v>
       </c>
-      <c r="I54" s="0" t="str">
+      <c r="I54" s="1" t="str">
         <f aca="false">IF(AND($D54&gt;0,$H54=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B55" s="0" t="str">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B55" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A55,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="0" t="n">
+      <c r="F55" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D55)</f>
         <v>7</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <f aca="false">IF($D55=0,0,$E55/$D55)</f>
         <v>0</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C55)</f>
         <v>9</v>
       </c>
-      <c r="I55" s="0" t="str">
+      <c r="I55" s="1" t="str">
         <f aca="false">IF(AND($D55&gt;0,$H55=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B56" s="0" t="str">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B56" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D56" s="0" t="n">
+      <c r="C56" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A56,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>8</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
         <v>0</v>
       </c>
-      <c r="F56" s="0" t="n">
+      <c r="F56" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D56)</f>
         <v>8</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="1" t="n">
         <f aca="false">IF($D56=0,0,$E56/$D56)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C56)</f>
         <v>11</v>
       </c>
-      <c r="I56" s="0" t="str">
+      <c r="I56" s="1" t="str">
         <f aca="false">IF(AND($D56&gt;0,$H56=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B57" s="0" t="str">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B57" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A57,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
         <v>2</v>
       </c>
-      <c r="F57" s="0" t="n">
+      <c r="F57" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D57)</f>
         <v>7</v>
       </c>
-      <c r="G57" s="0" t="n">
+      <c r="G57" s="1" t="n">
         <f aca="false">IF($D57=0,0,$E57/$D57)</f>
         <v>0.222222222222222</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C57)</f>
-        <v>10</v>
-      </c>
-      <c r="I57" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I57" s="1" t="str">
         <f aca="false">IF(AND($D57&gt;0,$H57=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B58" s="0" t="str">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B58" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D58" s="0" t="n">
+      <c r="D58" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A58,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
         <v>2</v>
       </c>
-      <c r="F58" s="0" t="n">
+      <c r="F58" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D58)</f>
         <v>3</v>
       </c>
-      <c r="G58" s="0" t="n">
+      <c r="G58" s="1" t="n">
         <f aca="false">IF($D58=0,0,$E58/$D58)</f>
         <v>0.4</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C58)</f>
         <v>20</v>
       </c>
-      <c r="I58" s="0" t="str">
+      <c r="I58" s="1" t="str">
         <f aca="false">IF(AND($D58&gt;0,$H58=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B59" s="0" t="str">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B59" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A59,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
         <v>4</v>
       </c>
-      <c r="F59" s="0" t="n">
+      <c r="F59" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D59)</f>
         <v>5</v>
       </c>
-      <c r="G59" s="0" t="n">
+      <c r="G59" s="1" t="n">
         <f aca="false">IF($D59=0,0,$E59/$D59)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C59)</f>
         <v>20</v>
       </c>
-      <c r="I59" s="0" t="str">
+      <c r="I59" s="1" t="str">
         <f aca="false">IF(AND($D59&gt;0,$H59=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B60" s="0" t="str">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B60" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A60,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
         <v>1</v>
       </c>
-      <c r="F60" s="0" t="n">
+      <c r="F60" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D60)</f>
         <v>5</v>
       </c>
-      <c r="G60" s="0" t="n">
+      <c r="G60" s="1" t="n">
         <f aca="false">IF($D60=0,0,$E60/$D60)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C60)</f>
         <v>18</v>
       </c>
-      <c r="I60" s="0" t="str">
+      <c r="I60" s="1" t="str">
         <f aca="false">IF(AND($D60&gt;0,$H60=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B61" s="0" t="str">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B61" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D61" s="0" t="n">
+      <c r="C61" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A61,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
         <v>1</v>
       </c>
-      <c r="F61" s="0" t="n">
+      <c r="F61" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D61)</f>
-        <v>5</v>
-      </c>
-      <c r="G61" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <f aca="false">IF($D61=0,0,$E61/$D61)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C61)</f>
-        <v>6</v>
-      </c>
-      <c r="I61" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I61" s="1" t="str">
         <f aca="false">IF(AND($D61&gt;0,$H61=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B62" s="0" t="str">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B62" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A62,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
         <v>2</v>
       </c>
-      <c r="F62" s="0" t="n">
+      <c r="F62" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D62)</f>
         <v>5</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="1" t="n">
         <f aca="false">IF($D62=0,0,$E62/$D62)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C62)</f>
         <v>17</v>
       </c>
-      <c r="I62" s="0" t="str">
+      <c r="I62" s="1" t="str">
         <f aca="false">IF(AND($D62&gt;0,$H62=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B63" s="0" t="str">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B63" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D63" s="0" t="n">
+      <c r="C63" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D63" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A63,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>15</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
         <v>6</v>
       </c>
-      <c r="F63" s="0" t="n">
+      <c r="F63" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D63)</f>
         <v>9</v>
       </c>
-      <c r="G63" s="0" t="n">
+      <c r="G63" s="1" t="n">
         <f aca="false">IF($D63=0,0,$E63/$D63)</f>
         <v>0.4</v>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C63)</f>
         <v>26</v>
       </c>
-      <c r="I63" s="0" t="str">
+      <c r="I63" s="1" t="str">
         <f aca="false">IF(AND($D63&gt;0,$H63=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B64" s="0" t="str">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B64" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D64" s="0" t="n">
+      <c r="C64" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D64" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A64,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>20</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
         <v>10</v>
       </c>
-      <c r="F64" s="0" t="n">
+      <c r="F64" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D64)</f>
         <v>10</v>
       </c>
-      <c r="G64" s="0" t="n">
+      <c r="G64" s="1" t="n">
         <f aca="false">IF($D64=0,0,$E64/$D64)</f>
         <v>0.5</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C64)</f>
         <v>40</v>
       </c>
-      <c r="I64" s="0" t="str">
+      <c r="I64" s="1" t="str">
         <f aca="false">IF(AND($D64&gt;0,$H64=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B65" s="0" t="str">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B65" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A65,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
         <v>0</v>
       </c>
-      <c r="F65" s="0" t="n">
+      <c r="F65" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D65)</f>
         <v>0</v>
       </c>
-      <c r="G65" s="0" t="n">
+      <c r="G65" s="1" t="n">
         <f aca="false">IF($D65=0,0,$E65/$D65)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C65)</f>
         <v>11</v>
       </c>
-      <c r="I65" s="0" t="str">
+      <c r="I65" s="1" t="str">
         <f aca="false">IF(AND($D65&gt;0,$H65=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B66" s="0" t="str">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B66" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C66" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D66" s="0" t="n">
+      <c r="C66" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D66" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A66,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
         <v>0</v>
       </c>
-      <c r="F66" s="0" t="n">
+      <c r="F66" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D66)</f>
         <v>0</v>
       </c>
-      <c r="G66" s="0" t="n">
+      <c r="G66" s="1" t="n">
         <f aca="false">IF($D66=0,0,$E66/$D66)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="0" t="n">
+      <c r="H66" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C66)</f>
         <v>20</v>
       </c>
-      <c r="I66" s="0" t="str">
+      <c r="I66" s="1" t="str">
         <f aca="false">IF(AND($D66&gt;0,$H66=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B67" s="0" t="str">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B67" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A67,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>25</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
         <v>4</v>
       </c>
-      <c r="F67" s="0" t="n">
+      <c r="F67" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D67)</f>
         <v>21</v>
       </c>
-      <c r="G67" s="0" t="n">
+      <c r="G67" s="1" t="n">
         <f aca="false">IF($D67=0,0,$E67/$D67)</f>
         <v>0.16</v>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C67)</f>
         <v>36</v>
       </c>
-      <c r="I67" s="0" t="str">
+      <c r="I67" s="1" t="str">
         <f aca="false">IF(AND($D67&gt;0,$H67=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B68" s="0" t="str">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B68" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D68" s="0" t="n">
+      <c r="D68" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A68,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
         <v>0</v>
       </c>
-      <c r="F68" s="0" t="n">
+      <c r="F68" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D68)</f>
         <v>7</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="1" t="n">
         <f aca="false">IF($D68=0,0,$E68/$D68)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C68)</f>
         <v>9</v>
       </c>
-      <c r="I68" s="0" t="str">
+      <c r="I68" s="1" t="str">
         <f aca="false">IF(AND($D68&gt;0,$H68=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B69" s="0" t="str">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B69" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D69" s="0" t="n">
+      <c r="C69" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D69" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A69,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
         <v>0</v>
       </c>
-      <c r="F69" s="0" t="n">
+      <c r="F69" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D69)</f>
         <v>7</v>
       </c>
-      <c r="G69" s="0" t="n">
+      <c r="G69" s="1" t="n">
         <f aca="false">IF($D69=0,0,$E69/$D69)</f>
         <v>0</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C69)</f>
         <v>11</v>
       </c>
-      <c r="I69" s="0" t="str">
+      <c r="I69" s="1" t="str">
         <f aca="false">IF(AND($D69&gt;0,$H69=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B70" s="0" t="str">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B70" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D70" s="0" t="n">
+      <c r="D70" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A70,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
         <v>2</v>
       </c>
-      <c r="F70" s="0" t="n">
+      <c r="F70" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D70)</f>
-        <v>8</v>
-      </c>
-      <c r="G70" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G70" s="1" t="n">
         <f aca="false">IF($D70=0,0,$E70/$D70)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C70)</f>
-        <v>10</v>
-      </c>
-      <c r="I70" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I70" s="1" t="str">
         <f aca="false">IF(AND($D70&gt;0,$H70=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B71" s="0" t="str">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B71" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A71,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
         <v>2</v>
       </c>
-      <c r="F71" s="0" t="n">
+      <c r="F71" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D71)</f>
         <v>4</v>
       </c>
-      <c r="G71" s="0" t="n">
+      <c r="G71" s="1" t="n">
         <f aca="false">IF($D71=0,0,$E71/$D71)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C71)</f>
         <v>20</v>
       </c>
-      <c r="I71" s="0" t="str">
+      <c r="I71" s="1" t="str">
         <f aca="false">IF(AND($D71&gt;0,$H71=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B72" s="0" t="str">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B72" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A72,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>10</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
         <v>5</v>
       </c>
-      <c r="F72" s="0" t="n">
+      <c r="F72" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D72)</f>
         <v>5</v>
       </c>
-      <c r="G72" s="0" t="n">
+      <c r="G72" s="1" t="n">
         <f aca="false">IF($D72=0,0,$E72/$D72)</f>
         <v>0.5</v>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C72)</f>
         <v>20</v>
       </c>
-      <c r="I72" s="0" t="str">
+      <c r="I72" s="1" t="str">
         <f aca="false">IF(AND($D72&gt;0,$H72=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B73" s="0" t="str">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B73" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A73,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
         <v>1</v>
       </c>
-      <c r="F73" s="0" t="n">
+      <c r="F73" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D73)</f>
         <v>6</v>
       </c>
-      <c r="G73" s="0" t="n">
+      <c r="G73" s="1" t="n">
         <f aca="false">IF($D73=0,0,$E73/$D73)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C73)</f>
         <v>18</v>
       </c>
-      <c r="I73" s="0" t="str">
+      <c r="I73" s="1" t="str">
         <f aca="false">IF(AND($D73&gt;0,$H73=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B74" s="0" t="str">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B74" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D74" s="0" t="n">
+      <c r="C74" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D74" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A74,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
         <v>1</v>
       </c>
-      <c r="F74" s="0" t="n">
+      <c r="F74" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D74)</f>
         <v>4</v>
       </c>
-      <c r="G74" s="0" t="n">
+      <c r="G74" s="1" t="n">
         <f aca="false">IF($D74=0,0,$E74/$D74)</f>
         <v>0.2</v>
       </c>
-      <c r="H74" s="0" t="n">
+      <c r="H74" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C74)</f>
-        <v>6</v>
-      </c>
-      <c r="I74" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I74" s="1" t="str">
         <f aca="false">IF(AND($D74&gt;0,$H74=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B75" s="0" t="str">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B75" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A75,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
         <v>2</v>
       </c>
-      <c r="F75" s="0" t="n">
+      <c r="F75" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D75)</f>
         <v>5</v>
       </c>
-      <c r="G75" s="0" t="n">
+      <c r="G75" s="1" t="n">
         <f aca="false">IF($D75=0,0,$E75/$D75)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H75" s="0" t="n">
+      <c r="H75" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C75)</f>
         <v>17</v>
       </c>
-      <c r="I75" s="0" t="str">
+      <c r="I75" s="1" t="str">
         <f aca="false">IF(AND($D75&gt;0,$H75=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B76" s="0" t="str">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B76" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D76" s="0" t="n">
+      <c r="C76" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D76" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A76,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
         <v>6</v>
       </c>
-      <c r="F76" s="0" t="n">
+      <c r="F76" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D76)</f>
         <v>7</v>
       </c>
-      <c r="G76" s="0" t="n">
+      <c r="G76" s="1" t="n">
         <f aca="false">IF($D76=0,0,$E76/$D76)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C76)</f>
         <v>26</v>
       </c>
-      <c r="I76" s="0" t="str">
+      <c r="I76" s="1" t="str">
         <f aca="false">IF(AND($D76&gt;0,$H76=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B77" s="0" t="str">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B77" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C77" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D77" s="0" t="n">
+      <c r="C77" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D77" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A77,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>22</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
         <v>11</v>
       </c>
-      <c r="F77" s="0" t="n">
+      <c r="F77" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D77)</f>
         <v>11</v>
       </c>
-      <c r="G77" s="0" t="n">
+      <c r="G77" s="1" t="n">
         <f aca="false">IF($D77=0,0,$E77/$D77)</f>
         <v>0.5</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C77)</f>
         <v>40</v>
       </c>
-      <c r="I77" s="0" t="str">
+      <c r="I77" s="1" t="str">
         <f aca="false">IF(AND($D77&gt;0,$H77=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B78" s="0" t="str">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B78" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A78,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
         <v>0</v>
       </c>
-      <c r="F78" s="0" t="n">
+      <c r="F78" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D78)</f>
         <v>0</v>
       </c>
-      <c r="G78" s="0" t="n">
+      <c r="G78" s="1" t="n">
         <f aca="false">IF($D78=0,0,$E78/$D78)</f>
         <v>0</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C78)</f>
         <v>11</v>
       </c>
-      <c r="I78" s="0" t="str">
+      <c r="I78" s="1" t="str">
         <f aca="false">IF(AND($D78&gt;0,$H78=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B79" s="0" t="str">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B79" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="C79" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D79" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A79,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
         <v>0</v>
       </c>
-      <c r="F79" s="0" t="n">
+      <c r="F79" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D79)</f>
         <v>0</v>
       </c>
-      <c r="G79" s="0" t="n">
+      <c r="G79" s="1" t="n">
         <f aca="false">IF($D79=0,0,$E79/$D79)</f>
         <v>0</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C79)</f>
         <v>20</v>
       </c>
-      <c r="I79" s="0" t="str">
+      <c r="I79" s="1" t="str">
         <f aca="false">IF(AND($D79&gt;0,$H79=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B80" s="0" t="str">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B80" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A80,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!E:E,MATCH($A80,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>28</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C80,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D80)</f>
         <v>4</v>
       </c>
-      <c r="F80" s="0" t="n">
+      <c r="F80" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C80,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D80)</f>
         <v>24</v>
       </c>
-      <c r="G80" s="0" t="n">
+      <c r="G80" s="1" t="n">
         <f aca="false">IF($D80=0,0,$E80/$D80)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C80)</f>
         <v>36</v>
       </c>
-      <c r="I80" s="0" t="str">
+      <c r="I80" s="1" t="str">
         <f aca="false">IF(AND($D80&gt;0,$H80=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B81" s="0" t="str">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B81" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A81,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D81" s="0" t="n">
+      <c r="D81" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!F:F,MATCH($A81,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C81,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D81)</f>
         <v>0</v>
       </c>
-      <c r="F81" s="0" t="n">
+      <c r="F81" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C81,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D81)</f>
         <v>6</v>
       </c>
-      <c r="G81" s="0" t="n">
+      <c r="G81" s="1" t="n">
         <f aca="false">IF($D81=0,0,$E81/$D81)</f>
         <v>0</v>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C81)</f>
         <v>9</v>
       </c>
-      <c r="I81" s="0" t="str">
+      <c r="I81" s="1" t="str">
         <f aca="false">IF(AND($D81&gt;0,$H81=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B82" s="0" t="str">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B82" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A82,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D82" s="0" t="n">
+      <c r="C82" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D82" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!G:G,MATCH($A82,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C82,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D82)</f>
         <v>0</v>
       </c>
-      <c r="F82" s="0" t="n">
+      <c r="F82" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C82,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D82)</f>
         <v>7</v>
       </c>
-      <c r="G82" s="0" t="n">
+      <c r="G82" s="1" t="n">
         <f aca="false">IF($D82=0,0,$E82/$D82)</f>
         <v>0</v>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C82)</f>
         <v>11</v>
       </c>
-      <c r="I82" s="0" t="str">
+      <c r="I82" s="1" t="str">
         <f aca="false">IF(AND($D82&gt;0,$H82=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B83" s="0" t="str">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B83" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A83,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D83" s="0" t="n">
+      <c r="D83" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!H:H,MATCH($A83,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>11</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C83,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D83)</f>
         <v>2</v>
       </c>
-      <c r="F83" s="0" t="n">
+      <c r="F83" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C83,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D83)</f>
-        <v>8</v>
-      </c>
-      <c r="G83" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" s="1" t="n">
         <f aca="false">IF($D83=0,0,$E83/$D83)</f>
         <v>0.181818181818182</v>
       </c>
-      <c r="H83" s="0" t="n">
+      <c r="H83" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C83)</f>
-        <v>10</v>
-      </c>
-      <c r="I83" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="I83" s="1" t="str">
         <f aca="false">IF(AND($D83&gt;0,$H83=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B84" s="0" t="str">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B84" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A84,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="D84" s="0" t="n">
+      <c r="D84" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!I:I,MATCH($A84,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>5</v>
       </c>
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C84,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D84)</f>
         <v>2</v>
       </c>
-      <c r="F84" s="0" t="n">
+      <c r="F84" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C84,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D84)</f>
         <v>3</v>
       </c>
-      <c r="G84" s="0" t="n">
+      <c r="G84" s="1" t="n">
         <f aca="false">IF($D84=0,0,$E84/$D84)</f>
         <v>0.4</v>
       </c>
-      <c r="H84" s="0" t="n">
+      <c r="H84" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C84)</f>
         <v>20</v>
       </c>
-      <c r="I84" s="0" t="str">
+      <c r="I84" s="1" t="str">
         <f aca="false">IF(AND($D84&gt;0,$H84=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B85" s="0" t="str">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B85" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A85,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="3" t="s">
         <v>1477</v>
       </c>
-      <c r="D85" s="0" t="n">
+      <c r="D85" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!J:J,MATCH($A85,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>9</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C85,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D85)</f>
         <v>4</v>
       </c>
-      <c r="F85" s="0" t="n">
+      <c r="F85" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C85,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D85)</f>
         <v>5</v>
       </c>
-      <c r="G85" s="0" t="n">
+      <c r="G85" s="1" t="n">
         <f aca="false">IF($D85=0,0,$E85/$D85)</f>
         <v>0.444444444444444</v>
       </c>
-      <c r="H85" s="0" t="n">
+      <c r="H85" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C85)</f>
         <v>20</v>
       </c>
-      <c r="I85" s="0" t="str">
+      <c r="I85" s="1" t="str">
         <f aca="false">IF(AND($D85&gt;0,$H85=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B86" s="0" t="str">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B86" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A86,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="3" t="s">
         <v>1484</v>
       </c>
-      <c r="D86" s="0" t="n">
+      <c r="D86" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!K:K,MATCH($A86,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E86" s="0" t="n">
+      <c r="E86" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C86,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D86)</f>
         <v>1</v>
       </c>
-      <c r="F86" s="0" t="n">
+      <c r="F86" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C86,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D86)</f>
         <v>5</v>
       </c>
-      <c r="G86" s="0" t="n">
+      <c r="G86" s="1" t="n">
         <f aca="false">IF($D86=0,0,$E86/$D86)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H86" s="0" t="n">
+      <c r="H86" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C86)</f>
         <v>18</v>
       </c>
-      <c r="I86" s="0" t="str">
+      <c r="I86" s="1" t="str">
         <f aca="false">IF(AND($D86&gt;0,$H86=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B87" s="0" t="str">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B87" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A87,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C87" s="13" t="s">
-        <v>1851</v>
-      </c>
-      <c r="D87" s="0" t="n">
+      <c r="C87" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D87" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!L:L,MATCH($A87,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>7</v>
       </c>
-      <c r="E87" s="0" t="n">
+      <c r="E87" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C87,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D87)</f>
         <v>1</v>
       </c>
-      <c r="F87" s="0" t="n">
+      <c r="F87" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C87,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D87)</f>
-        <v>5</v>
-      </c>
-      <c r="G87" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" s="1" t="n">
         <f aca="false">IF($D87=0,0,$E87/$D87)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="H87" s="0" t="n">
+      <c r="H87" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C87)</f>
-        <v>6</v>
-      </c>
-      <c r="I87" s="0" t="str">
+        <v>7</v>
+      </c>
+      <c r="I87" s="1" t="str">
         <f aca="false">IF(AND($D87&gt;0,$H87=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B88" s="0" t="str">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B88" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A88,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="3" t="s">
         <v>1481</v>
       </c>
-      <c r="D88" s="0" t="n">
+      <c r="D88" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!M:M,MATCH($A88,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>6</v>
       </c>
-      <c r="E88" s="0" t="n">
+      <c r="E88" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C88,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D88)</f>
         <v>2</v>
       </c>
-      <c r="F88" s="0" t="n">
+      <c r="F88" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C88,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D88)</f>
         <v>4</v>
       </c>
-      <c r="G88" s="0" t="n">
+      <c r="G88" s="1" t="n">
         <f aca="false">IF($D88=0,0,$E88/$D88)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="H88" s="0" t="n">
+      <c r="H88" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C88)</f>
         <v>17</v>
       </c>
-      <c r="I88" s="0" t="str">
+      <c r="I88" s="1" t="str">
         <f aca="false">IF(AND($D88&gt;0,$H88=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B89" s="0" t="str">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B89" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A89,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C89" s="13" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D89" s="0" t="n">
+      <c r="C89" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D89" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!N:N,MATCH($A89,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>13</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E89" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C89,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D89)</f>
         <v>6</v>
       </c>
-      <c r="F89" s="0" t="n">
+      <c r="F89" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C89,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D89)</f>
         <v>7</v>
       </c>
-      <c r="G89" s="0" t="n">
+      <c r="G89" s="1" t="n">
         <f aca="false">IF($D89=0,0,$E89/$D89)</f>
         <v>0.461538461538462</v>
       </c>
-      <c r="H89" s="0" t="n">
+      <c r="H89" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C89)</f>
         <v>26</v>
       </c>
-      <c r="I89" s="0" t="str">
+      <c r="I89" s="1" t="str">
         <f aca="false">IF(AND($D89&gt;0,$H89=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B90" s="0" t="str">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B90" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A90,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D90" s="0" t="n">
+      <c r="C90" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D90" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!O:O,MATCH($A90,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>21</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E90" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C90,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D90)</f>
         <v>11</v>
       </c>
-      <c r="F90" s="0" t="n">
+      <c r="F90" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C90,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D90)</f>
         <v>10</v>
       </c>
-      <c r="G90" s="0" t="n">
+      <c r="G90" s="1" t="n">
         <f aca="false">IF($D90=0,0,$E90/$D90)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="H90" s="0" t="n">
+      <c r="H90" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C90)</f>
         <v>40</v>
       </c>
-      <c r="I90" s="0" t="str">
+      <c r="I90" s="1" t="str">
         <f aca="false">IF(AND($D90&gt;0,$H90=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B91" s="0" t="str">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B91" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A91,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D91" s="0" t="n">
+      <c r="D91" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!P:P,MATCH($A91,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E91" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C91,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D91)</f>
         <v>0</v>
       </c>
-      <c r="F91" s="0" t="n">
+      <c r="F91" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C91,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D91)</f>
         <v>0</v>
       </c>
-      <c r="G91" s="0" t="n">
+      <c r="G91" s="1" t="n">
         <f aca="false">IF($D91=0,0,$E91/$D91)</f>
         <v>0</v>
       </c>
-      <c r="H91" s="0" t="n">
+      <c r="H91" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C91)</f>
         <v>11</v>
       </c>
-      <c r="I91" s="0" t="str">
+      <c r="I91" s="1" t="str">
         <f aca="false">IF(AND($D91&gt;0,$H91=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="13" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B92" s="0" t="str">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B92" s="1" t="str">
         <f aca="false">INDEX('סקרים לפי ערוץ'!$B:$B,MATCH($A92,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>2026-10-27</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D92" s="0" t="n">
+      <c r="C92" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D92" s="1" t="n">
         <f aca="false">INDEX('סקרים לפי ערוץ'!Q:Q,MATCH($A92,'סקרים לפי ערוץ'!$A:$A,0))</f>
         <v>0</v>
       </c>
-      <c r="E92" s="0" t="n">
+      <c r="E92" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C92,'מועמדים 2026'!$D:$D,"נ",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D92)</f>
         <v>0</v>
       </c>
-      <c r="F92" s="0" t="n">
+      <c r="F92" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C92,'מועמדים 2026'!$D:$D,"ז",'מועמדים 2026'!$B:$B,"&lt;="&amp;$D92)</f>
         <v>0</v>
       </c>
-      <c r="G92" s="0" t="n">
+      <c r="G92" s="1" t="n">
         <f aca="false">IF($D92=0,0,$E92/$D92)</f>
         <v>0</v>
       </c>
-      <c r="H92" s="0" t="n">
+      <c r="H92" s="1" t="n">
         <f aca="false">COUNTIFS('מועמדים 2026'!$A:$A,$C92)</f>
         <v>20</v>
       </c>
-      <c r="I92" s="0" t="str">
+      <c r="I92" s="1" t="str">
         <f aca="false">IF(AND($D92&gt;0,$H92=0),"אין נתוני מועמדים לחישוב","")</f>
         <v/>
       </c>
